--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39D40477-0DE8-4624-8F95-684C536B9D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A94822-BC13-4A8D-AD04-7A9933C61229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="0" windowWidth="33540" windowHeight="20340" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-150" yWindow="0" windowWidth="30255" windowHeight="20985" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -147,6 +147,12 @@
     <t>Tiffany Lewis</t>
   </si>
   <si>
+    <t>Connor Floriani</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
     <t>ManagerName</t>
   </si>
   <si>
@@ -228,20 +234,14 @@
     <t>tiffany.lewis1@lplfinancial.com</t>
   </si>
   <si>
-    <t>Connor Floriani</t>
-  </si>
-  <si>
     <t>Connor.Floriani@lplfinancial.com</t>
-  </si>
-  <si>
-    <t>September</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,12 +260,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -307,9 +301,9 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,8 +349,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I335" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I335" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I350" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I350" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
@@ -706,7 +700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I335"/>
+  <dimension ref="A1:I350"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
@@ -10176,13 +10170,13 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C327" s="5">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>11</v>
@@ -10191,13 +10185,13 @@
         <v>12</v>
       </c>
       <c r="F327" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G327" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I327" s="1">
         <v>2026</v>
@@ -10205,28 +10199,28 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C328" s="5">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F328" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G328" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I328" s="1">
         <v>2026</v>
@@ -10234,13 +10228,13 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C329" s="5">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>11</v>
@@ -10249,13 +10243,13 @@
         <v>12</v>
       </c>
       <c r="F329" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G329" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H329" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I329" s="1">
         <v>2026</v>
@@ -10263,16 +10257,16 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C330" s="5">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>12</v>
@@ -10284,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="H330" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I330" s="1">
         <v>2026</v>
@@ -10292,13 +10286,13 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C331" s="5">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>11</v>
@@ -10307,13 +10301,13 @@
         <v>12</v>
       </c>
       <c r="F331" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G331" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H331" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I331" s="1">
         <v>2026</v>
@@ -10321,28 +10315,28 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C332" s="5">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F332" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G332" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H332" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I332" s="1">
         <v>2026</v>
@@ -10350,93 +10344,527 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C333" s="5">
+        <v>46267</v>
+      </c>
+      <c r="D333" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E333" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F333" s="1">
+        <v>100</v>
+      </c>
+      <c r="G333" s="2">
+        <v>1</v>
+      </c>
+      <c r="H333" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I333" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B334" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D334" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E334" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F334" s="1">
+        <v>95</v>
+      </c>
+      <c r="G334" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H334" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I334" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B335" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="5">
+        <v>46274</v>
+      </c>
+      <c r="D335" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E335" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F335" s="1">
+        <v>100</v>
+      </c>
+      <c r="G335" s="6">
+        <v>1</v>
+      </c>
+      <c r="H335" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I335" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B336" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D336" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E336" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F336" s="1">
+        <v>100</v>
+      </c>
+      <c r="G336" s="6">
+        <v>1</v>
+      </c>
+      <c r="H336" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I336" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B337" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C337" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D337" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E337" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F337" s="1">
+        <v>95</v>
+      </c>
+      <c r="G337" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H337" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I337" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B338" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C338" s="5">
+        <v>46274</v>
+      </c>
+      <c r="D338" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E338" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F338" s="1">
+        <v>95</v>
+      </c>
+      <c r="G338" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H338" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I338" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B339" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C339" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D339" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E339" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F339" s="1">
+        <v>100</v>
+      </c>
+      <c r="G339" s="6">
+        <v>1</v>
+      </c>
+      <c r="H339" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I339" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B340" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C340" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D340" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E340" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F340" s="1">
+        <v>95</v>
+      </c>
+      <c r="G340" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H340" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I340" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C341" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D341" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E341" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F341" s="1">
+        <v>100</v>
+      </c>
+      <c r="G341" s="6">
+        <v>1</v>
+      </c>
+      <c r="H341" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I341" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B342" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C342" s="5">
+        <v>46274</v>
+      </c>
+      <c r="D342" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E342" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F342" s="1">
+        <v>85</v>
+      </c>
+      <c r="G342" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="H342" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I342" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B343" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C343" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D343" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E343" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F343" s="1">
+        <v>100</v>
+      </c>
+      <c r="G343" s="6">
+        <v>1</v>
+      </c>
+      <c r="H343" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I343" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B344" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C344" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D344" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E344" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F344" s="1">
+        <v>95</v>
+      </c>
+      <c r="G344" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H344" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I344" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C333" s="5">
-        <v>46268</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E333" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F333" s="1">
-        <v>100</v>
-      </c>
-      <c r="G333" s="2">
-        <v>1</v>
-      </c>
-      <c r="H333" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I333" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A334" t="s">
-        <v>15</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C334" s="7">
-        <v>46267</v>
-      </c>
-      <c r="D334" t="s">
-        <v>11</v>
-      </c>
-      <c r="E334" t="s">
-        <v>12</v>
-      </c>
-      <c r="F334" s="8">
+      <c r="B345" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C345" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D345" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E345" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F345" s="1">
+        <v>100</v>
+      </c>
+      <c r="G345" s="6">
+        <v>1</v>
+      </c>
+      <c r="H345" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I345" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B346" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C346" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D346" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E346" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F346" s="1">
+        <v>100</v>
+      </c>
+      <c r="G346" s="6">
+        <v>1</v>
+      </c>
+      <c r="H346" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I346" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B347" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C347" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D347" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E347" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F347" s="1">
         <v>90</v>
       </c>
-      <c r="G334" s="6">
+      <c r="G347" s="6">
         <v>0.9</v>
       </c>
-      <c r="H334" t="s">
-        <v>65</v>
-      </c>
-      <c r="I334" s="1">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A335" t="s">
+      <c r="H347" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I347" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B335" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C335" s="7">
-        <v>46268</v>
-      </c>
-      <c r="D335" t="s">
-        <v>11</v>
-      </c>
-      <c r="E335" t="s">
-        <v>12</v>
-      </c>
-      <c r="F335" s="8">
-        <v>100</v>
-      </c>
-      <c r="G335" s="6">
-        <v>1</v>
-      </c>
-      <c r="H335" t="s">
-        <v>65</v>
-      </c>
-      <c r="I335" s="1">
+      <c r="B348" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C348" s="5">
+        <v>46276</v>
+      </c>
+      <c r="D348" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E348" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F348" s="1">
+        <v>100</v>
+      </c>
+      <c r="G348" s="6">
+        <v>1</v>
+      </c>
+      <c r="H348" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I348" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B349" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C349" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D349" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E349" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F349" s="1">
+        <v>95</v>
+      </c>
+      <c r="G349" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H349" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I349" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B350" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C350" s="5">
+        <v>46274</v>
+      </c>
+      <c r="D350" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E350" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F350" s="1">
+        <v>100</v>
+      </c>
+      <c r="G350" s="6">
+        <v>1</v>
+      </c>
+      <c r="H350" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I350" s="1">
         <v>2026</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
@@ -10464,13 +10892,13 @@
         <v>1</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -10481,13 +10909,13 @@
         <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -10498,13 +10926,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -10515,13 +10943,13 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -10532,13 +10960,13 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -10549,13 +10977,13 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -10566,13 +10994,13 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -10583,13 +11011,13 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -10600,30 +11028,30 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
         <v>51</v>
       </c>
-      <c r="B10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -10634,13 +11062,13 @@
         <v>10</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -10651,13 +11079,13 @@
         <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -10668,13 +11096,13 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -10685,13 +11113,13 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -10702,13 +11130,13 @@
         <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -10719,13 +11147,13 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -10736,13 +11164,13 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -10753,13 +11181,13 @@
         <v>19</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -10770,13 +11198,13 @@
         <v>10</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -10787,30 +11215,30 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
         <v>19</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -10823,8 +11251,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7f98047a509e9e082d0d58dfbe71352c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="361f48e45990901628f9319c45e78890" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bbf009f58139d30e700e9d9dd8708ee">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bbfb5a56ff61f0f4bba1626b54b38306" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <xsd:import namespace="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <xsd:element name="properties">
@@ -10849,6 +11286,7 @@
                 <xsd:element ref="ns2:Status" minOccurs="0"/>
                 <xsd:element ref="ns2:Notes" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -10930,6 +11368,11 @@
     <xsd:element name="MediaServiceBillingMetadata" ma:index="24" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_Flow_SignoffStatus" ma:index="25" nillable="true" ma:displayName="Sign-off status" ma:internalName="_x0024_Resources_x003a_core_x002c_Signoff_Status">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -11073,15 +11516,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11091,12 +11525,21 @@
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
     <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95F4425-7749-4603-B4BA-980799E13416}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B400D-C15B-4808-975D-D6FB017A04F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -11114,26 +11557,18 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A94822-BC13-4A8D-AD04-7A9933C61229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AF3DD3-7B93-49F0-8884-8528CF69AE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="0" windowWidth="30255" windowHeight="20985" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="25260" yWindow="45" windowWidth="26445" windowHeight="20340" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1859" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -294,27 +294,35 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="12">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -335,6 +343,37 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -349,28 +388,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I350" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I350" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I357" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:I357" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
     <sortCondition ref="C1:C196"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
-    <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
-    <tableColumn id="3" xr3:uid="{6551223E-2902-4D9E-887E-72F4C30CFEBB}" name="DateOfCall"/>
-    <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact"/>
-    <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed"/>
-    <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore"/>
-    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="1" dataCellStyle="Percent"/>
-    <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth"/>
-    <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear"/>
+    <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{6551223E-2902-4D9E-887E-72F4C30CFEBB}" name="DateOfCall" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="4" dataCellStyle="Percent"/>
+    <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="11">
   <autoFilter ref="A1:E21" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
@@ -700,18 +739,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I350"/>
+  <dimension ref="A1:I357"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -750,7 +789,7 @@
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>46113</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -779,7 +818,7 @@
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>46113</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -808,7 +847,7 @@
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>46113</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -837,7 +876,7 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>46113</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -866,7 +905,7 @@
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>46113</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -895,7 +934,7 @@
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>46114</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -924,7 +963,7 @@
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>46114</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -953,7 +992,7 @@
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>46114</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -982,7 +1021,7 @@
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>46118</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1011,7 +1050,7 @@
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>46118</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1040,7 +1079,7 @@
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>46119</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1069,7 +1108,7 @@
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>46119</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1098,7 +1137,7 @@
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>46119</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1127,7 +1166,7 @@
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>46120</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1156,7 +1195,7 @@
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>46120</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1185,7 +1224,7 @@
       <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>46120</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1214,7 +1253,7 @@
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>46120</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1243,7 +1282,7 @@
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>46121</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1272,7 +1311,7 @@
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>46121</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1301,7 +1340,7 @@
       <c r="B21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>46121</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1330,7 +1369,7 @@
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>46121</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1359,7 +1398,7 @@
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>46122</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -1388,7 +1427,7 @@
       <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>46122</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1417,7 +1456,7 @@
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>46122</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1446,7 +1485,7 @@
       <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>46122</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1475,7 +1514,7 @@
       <c r="B27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>46125</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1504,7 +1543,7 @@
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>46126</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1533,7 +1572,7 @@
       <c r="B29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>46126</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1562,7 +1601,7 @@
       <c r="B30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>46126</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1591,7 +1630,7 @@
       <c r="B31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4">
         <v>46127</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1620,7 +1659,7 @@
       <c r="B32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="4">
         <v>46127</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1649,7 +1688,7 @@
       <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="4">
         <v>46127</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1678,7 +1717,7 @@
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>46127</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -1707,7 +1746,7 @@
       <c r="B35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4">
         <v>46128</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -1736,7 +1775,7 @@
       <c r="B36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4">
         <v>46128</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -1765,7 +1804,7 @@
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="4">
         <v>46128</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -1794,7 +1833,7 @@
       <c r="B38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="4">
         <v>46128</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -1823,7 +1862,7 @@
       <c r="B39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="4">
         <v>46129</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -1852,7 +1891,7 @@
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4">
         <v>46129</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -1881,7 +1920,7 @@
       <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="4">
         <v>46129</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -1910,7 +1949,7 @@
       <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="4">
         <v>46133</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -1939,7 +1978,7 @@
       <c r="B43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="4">
         <v>46134</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -1968,7 +2007,7 @@
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="4">
         <v>46134</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -1997,7 +2036,7 @@
       <c r="B45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="4">
         <v>46134</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2026,7 +2065,7 @@
       <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="4">
         <v>46135</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2055,7 +2094,7 @@
       <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="4">
         <v>46135</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2084,7 +2123,7 @@
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="4">
         <v>46135</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2113,7 +2152,7 @@
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="4">
         <v>46135</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2142,7 +2181,7 @@
       <c r="B50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="4">
         <v>46135</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2171,7 +2210,7 @@
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="4">
         <v>46135</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2200,7 +2239,7 @@
       <c r="B52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="4">
         <v>46135</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2229,7 +2268,7 @@
       <c r="B53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="5">
+      <c r="C53" s="4">
         <v>46140</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2258,7 +2297,7 @@
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="5">
+      <c r="C54" s="4">
         <v>46140</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -2287,7 +2326,7 @@
       <c r="B55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="5">
+      <c r="C55" s="4">
         <v>46141</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -2316,7 +2355,7 @@
       <c r="B56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="4">
         <v>46141</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -2345,7 +2384,7 @@
       <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="5">
+      <c r="C57" s="4">
         <v>46141</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -2374,7 +2413,7 @@
       <c r="B58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="5">
+      <c r="C58" s="4">
         <v>46141</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -2403,7 +2442,7 @@
       <c r="B59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="5">
+      <c r="C59" s="4">
         <v>46141</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2432,7 +2471,7 @@
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="4">
         <v>46142</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -2461,7 +2500,7 @@
       <c r="B61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="5">
+      <c r="C61" s="4">
         <v>46142</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -2490,7 +2529,7 @@
       <c r="B62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="4">
         <v>46142</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -2519,7 +2558,7 @@
       <c r="B63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="5">
+      <c r="C63" s="4">
         <v>46142</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -2548,7 +2587,7 @@
       <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="4">
         <v>46142</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -2577,7 +2616,7 @@
       <c r="B65" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="5">
+      <c r="C65" s="4">
         <v>46142</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -2606,7 +2645,7 @@
       <c r="B66" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="4">
         <v>46142</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -2635,7 +2674,7 @@
       <c r="B67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="5">
+      <c r="C67" s="4">
         <v>46143</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -2664,7 +2703,7 @@
       <c r="B68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="4">
         <v>46143</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -2693,7 +2732,7 @@
       <c r="B69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="5">
+      <c r="C69" s="4">
         <v>46147</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -2722,7 +2761,7 @@
       <c r="B70" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C70" s="5">
+      <c r="C70" s="4">
         <v>46147</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -2751,7 +2790,7 @@
       <c r="B71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="4">
         <v>46147</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -2780,7 +2819,7 @@
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="4">
         <v>46148</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -2809,7 +2848,7 @@
       <c r="B73" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C73" s="5">
+      <c r="C73" s="4">
         <v>46148</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -2838,7 +2877,7 @@
       <c r="B74" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="4">
         <v>46148</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -2867,7 +2906,7 @@
       <c r="B75" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="5">
+      <c r="C75" s="4">
         <v>46148</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -2896,7 +2935,7 @@
       <c r="B76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="4">
         <v>46149</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -2925,7 +2964,7 @@
       <c r="B77" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="4">
         <v>46149</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -2954,7 +2993,7 @@
       <c r="B78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="4">
         <v>46149</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -2983,7 +3022,7 @@
       <c r="B79" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="4">
         <v>46149</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3012,7 +3051,7 @@
       <c r="B80" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C80" s="5">
+      <c r="C80" s="4">
         <v>46149</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3041,7 +3080,7 @@
       <c r="B81" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C81" s="5">
+      <c r="C81" s="4">
         <v>46149</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3070,7 +3109,7 @@
       <c r="B82" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="4">
         <v>46149</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3099,7 +3138,7 @@
       <c r="B83" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C83" s="5">
+      <c r="C83" s="4">
         <v>46150</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3128,7 +3167,7 @@
       <c r="B84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="4">
         <v>46153</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3157,7 +3196,7 @@
       <c r="B85" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C85" s="5">
+      <c r="C85" s="4">
         <v>46154</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3186,7 +3225,7 @@
       <c r="B86" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="5">
+      <c r="C86" s="4">
         <v>46154</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3215,7 +3254,7 @@
       <c r="B87" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="4">
         <v>46154</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3244,7 +3283,7 @@
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="4">
         <v>46154</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3273,7 +3312,7 @@
       <c r="B89" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="4">
         <v>46155</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3302,7 +3341,7 @@
       <c r="B90" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="4">
         <v>46155</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3331,7 +3370,7 @@
       <c r="B91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="5">
+      <c r="C91" s="4">
         <v>46155</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3360,7 +3399,7 @@
       <c r="B92" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="4">
         <v>46155</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3389,7 +3428,7 @@
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="4">
         <v>46156</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3418,7 +3457,7 @@
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="4">
         <v>46156</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3447,7 +3486,7 @@
       <c r="B95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="4">
         <v>46156</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3476,7 +3515,7 @@
       <c r="B96" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C96" s="5">
+      <c r="C96" s="4">
         <v>46156</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3505,7 +3544,7 @@
       <c r="B97" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="5">
+      <c r="C97" s="4">
         <v>46157</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3534,7 +3573,7 @@
       <c r="B98" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="4">
         <v>46157</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3563,7 +3602,7 @@
       <c r="B99" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="5">
+      <c r="C99" s="4">
         <v>46157</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3592,7 +3631,7 @@
       <c r="B100" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C100" s="5">
+      <c r="C100" s="4">
         <v>46161</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3621,7 +3660,7 @@
       <c r="B101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C101" s="5">
+      <c r="C101" s="4">
         <v>46162</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3650,7 +3689,7 @@
       <c r="B102" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="5">
+      <c r="C102" s="4">
         <v>46168</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3679,7 +3718,7 @@
       <c r="B103" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C103" s="5">
+      <c r="C103" s="4">
         <v>46168</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3708,7 +3747,7 @@
       <c r="B104" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C104" s="5">
+      <c r="C104" s="4">
         <v>46168</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3737,7 +3776,7 @@
       <c r="B105" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="5">
+      <c r="C105" s="4">
         <v>46169</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3766,7 +3805,7 @@
       <c r="B106" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="5">
+      <c r="C106" s="4">
         <v>46169</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3795,7 +3834,7 @@
       <c r="B107" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C107" s="5">
+      <c r="C107" s="4">
         <v>46170</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -3824,7 +3863,7 @@
       <c r="B108" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C108" s="4">
         <v>46170</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3853,7 +3892,7 @@
       <c r="B109" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C109" s="5">
+      <c r="C109" s="4">
         <v>46170</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3882,7 +3921,7 @@
       <c r="B110" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C110" s="5">
+      <c r="C110" s="4">
         <v>46170</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3911,7 +3950,7 @@
       <c r="B111" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="5">
+      <c r="C111" s="4">
         <v>46170</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3940,7 +3979,7 @@
       <c r="B112" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="5">
+      <c r="C112" s="4">
         <v>46171</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -3969,7 +4008,7 @@
       <c r="B113" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C113" s="5">
+      <c r="C113" s="4">
         <v>46171</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -3998,7 +4037,7 @@
       <c r="B114" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C114" s="5">
+      <c r="C114" s="4">
         <v>46171</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4027,7 +4066,7 @@
       <c r="B115" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C115" s="5">
+      <c r="C115" s="4">
         <v>46174</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -4056,7 +4095,7 @@
       <c r="B116" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C116" s="4">
         <v>46174</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -4085,7 +4124,7 @@
       <c r="B117" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C117" s="5">
+      <c r="C117" s="4">
         <v>46174</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -4114,7 +4153,7 @@
       <c r="B118" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C118" s="5">
+      <c r="C118" s="4">
         <v>46175</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4143,7 +4182,7 @@
       <c r="B119" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C119" s="5">
+      <c r="C119" s="4">
         <v>46175</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4172,7 +4211,7 @@
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="4">
         <v>46176</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4201,7 +4240,7 @@
       <c r="B121" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C121" s="5">
+      <c r="C121" s="4">
         <v>46176</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4230,7 +4269,7 @@
       <c r="B122" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C122" s="5">
+      <c r="C122" s="4">
         <v>46177</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4259,7 +4298,7 @@
       <c r="B123" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C123" s="5">
+      <c r="C123" s="4">
         <v>46178</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -4288,7 +4327,7 @@
       <c r="B124" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C124" s="5">
+      <c r="C124" s="4">
         <v>46178</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -4317,7 +4356,7 @@
       <c r="B125" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C125" s="5">
+      <c r="C125" s="4">
         <v>46178</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -4346,7 +4385,7 @@
       <c r="B126" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C126" s="5">
+      <c r="C126" s="4">
         <v>46178</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4375,7 +4414,7 @@
       <c r="B127" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C127" s="5">
+      <c r="C127" s="4">
         <v>46178</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4404,7 +4443,7 @@
       <c r="B128" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C128" s="5">
+      <c r="C128" s="4">
         <v>46178</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4433,7 +4472,7 @@
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C129" s="5">
+      <c r="C129" s="4">
         <v>46181</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -4462,7 +4501,7 @@
       <c r="B130" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C130" s="5">
+      <c r="C130" s="4">
         <v>46181</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -4491,7 +4530,7 @@
       <c r="B131" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C131" s="5">
+      <c r="C131" s="4">
         <v>46181</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -4520,7 +4559,7 @@
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C132" s="5">
+      <c r="C132" s="4">
         <v>46182</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -4549,7 +4588,7 @@
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C133" s="5">
+      <c r="C133" s="4">
         <v>46182</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -4578,7 +4617,7 @@
       <c r="B134" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C134" s="5">
+      <c r="C134" s="4">
         <v>46182</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -4607,7 +4646,7 @@
       <c r="B135" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C135" s="5">
+      <c r="C135" s="4">
         <v>46182</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -4636,7 +4675,7 @@
       <c r="B136" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C136" s="5">
+      <c r="C136" s="4">
         <v>46182</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -4665,7 +4704,7 @@
       <c r="B137" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C137" s="5">
+      <c r="C137" s="4">
         <v>46182</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -4694,7 +4733,7 @@
       <c r="B138" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C138" s="5">
+      <c r="C138" s="4">
         <v>46182</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -4723,7 +4762,7 @@
       <c r="B139" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="5">
+      <c r="C139" s="4">
         <v>46182</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -4752,7 +4791,7 @@
       <c r="B140" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C140" s="5">
+      <c r="C140" s="4">
         <v>46182</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -4781,7 +4820,7 @@
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="5">
+      <c r="C141" s="4">
         <v>46183</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -4810,7 +4849,7 @@
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C142" s="5">
+      <c r="C142" s="4">
         <v>46183</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -4839,7 +4878,7 @@
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C143" s="5">
+      <c r="C143" s="4">
         <v>46184</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -4868,7 +4907,7 @@
       <c r="B144" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="5">
+      <c r="C144" s="4">
         <v>46184</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -4897,7 +4936,7 @@
       <c r="B145" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C145" s="5">
+      <c r="C145" s="4">
         <v>46184</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -4926,7 +4965,7 @@
       <c r="B146" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C146" s="5">
+      <c r="C146" s="4">
         <v>46184</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -4955,7 +4994,7 @@
       <c r="B147" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C147" s="5">
+      <c r="C147" s="4">
         <v>46184</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -4984,7 +5023,7 @@
       <c r="B148" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="5">
+      <c r="C148" s="4">
         <v>46184</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -5013,7 +5052,7 @@
       <c r="B149" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C149" s="5">
+      <c r="C149" s="4">
         <v>46184</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -5042,7 +5081,7 @@
       <c r="B150" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C150" s="5">
+      <c r="C150" s="4">
         <v>46185</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -5071,7 +5110,7 @@
       <c r="B151" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C151" s="5">
+      <c r="C151" s="4">
         <v>46185</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -5100,7 +5139,7 @@
       <c r="B152" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="5">
+      <c r="C152" s="4">
         <v>46188</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -5129,7 +5168,7 @@
       <c r="B153" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="5">
+      <c r="C153" s="4">
         <v>46188</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -5158,7 +5197,7 @@
       <c r="B154" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C154" s="5">
+      <c r="C154" s="4">
         <v>46188</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -5187,7 +5226,7 @@
       <c r="B155" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C155" s="5">
+      <c r="C155" s="4">
         <v>46188</v>
       </c>
       <c r="D155" s="1" t="s">
@@ -5216,7 +5255,7 @@
       <c r="B156" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C156" s="5">
+      <c r="C156" s="4">
         <v>46188</v>
       </c>
       <c r="D156" s="1" t="s">
@@ -5245,7 +5284,7 @@
       <c r="B157" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C157" s="5">
+      <c r="C157" s="4">
         <v>46188</v>
       </c>
       <c r="D157" s="1" t="s">
@@ -5274,7 +5313,7 @@
       <c r="B158" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C158" s="5">
+      <c r="C158" s="4">
         <v>46188</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -5303,7 +5342,7 @@
       <c r="B159" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C159" s="5">
+      <c r="C159" s="4">
         <v>46188</v>
       </c>
       <c r="D159" s="1" t="s">
@@ -5332,7 +5371,7 @@
       <c r="B160" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C160" s="5">
+      <c r="C160" s="4">
         <v>46189</v>
       </c>
       <c r="D160" s="1" t="s">
@@ -5361,7 +5400,7 @@
       <c r="B161" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C161" s="5">
+      <c r="C161" s="4">
         <v>46189</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -5390,7 +5429,7 @@
       <c r="B162" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="5">
+      <c r="C162" s="4">
         <v>46189</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -5419,7 +5458,7 @@
       <c r="B163" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C163" s="5">
+      <c r="C163" s="4">
         <v>46189</v>
       </c>
       <c r="D163" s="1" t="s">
@@ -5448,7 +5487,7 @@
       <c r="B164" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C164" s="5">
+      <c r="C164" s="4">
         <v>46190</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -5477,7 +5516,7 @@
       <c r="B165" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C165" s="5">
+      <c r="C165" s="4">
         <v>46190</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -5506,7 +5545,7 @@
       <c r="B166" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C166" s="5">
+      <c r="C166" s="4">
         <v>46190</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -5535,7 +5574,7 @@
       <c r="B167" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C167" s="5">
+      <c r="C167" s="4">
         <v>46191</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -5564,7 +5603,7 @@
       <c r="B168" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C168" s="5">
+      <c r="C168" s="4">
         <v>46191</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -5593,7 +5632,7 @@
       <c r="B169" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C169" s="5">
+      <c r="C169" s="4">
         <v>46191</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -5622,7 +5661,7 @@
       <c r="B170" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C170" s="5">
+      <c r="C170" s="4">
         <v>46191</v>
       </c>
       <c r="D170" s="1" t="s">
@@ -5651,7 +5690,7 @@
       <c r="B171" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C171" s="5">
+      <c r="C171" s="4">
         <v>46191</v>
       </c>
       <c r="D171" s="1" t="s">
@@ -5680,7 +5719,7 @@
       <c r="B172" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C172" s="5">
+      <c r="C172" s="4">
         <v>46191</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -5709,7 +5748,7 @@
       <c r="B173" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C173" s="5">
+      <c r="C173" s="4">
         <v>46195</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -5738,7 +5777,7 @@
       <c r="B174" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C174" s="5">
+      <c r="C174" s="4">
         <v>46196</v>
       </c>
       <c r="D174" s="1" t="s">
@@ -5767,7 +5806,7 @@
       <c r="B175" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C175" s="5">
+      <c r="C175" s="4">
         <v>46197</v>
       </c>
       <c r="D175" s="1" t="s">
@@ -5796,7 +5835,7 @@
       <c r="B176" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C176" s="5">
+      <c r="C176" s="4">
         <v>46197</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -5825,7 +5864,7 @@
       <c r="B177" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C177" s="5">
+      <c r="C177" s="4">
         <v>46198</v>
       </c>
       <c r="D177" s="1" t="s">
@@ -5854,7 +5893,7 @@
       <c r="B178" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C178" s="5">
+      <c r="C178" s="4">
         <v>46198</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -5883,7 +5922,7 @@
       <c r="B179" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C179" s="5">
+      <c r="C179" s="4">
         <v>46198</v>
       </c>
       <c r="D179" s="1" t="s">
@@ -5912,7 +5951,7 @@
       <c r="B180" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C180" s="5">
+      <c r="C180" s="4">
         <v>46198</v>
       </c>
       <c r="D180" s="1" t="s">
@@ -5941,7 +5980,7 @@
       <c r="B181" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C181" s="5">
+      <c r="C181" s="4">
         <v>46198</v>
       </c>
       <c r="D181" s="1" t="s">
@@ -5970,7 +6009,7 @@
       <c r="B182" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C182" s="5">
+      <c r="C182" s="4">
         <v>46198</v>
       </c>
       <c r="D182" s="1" t="s">
@@ -5999,7 +6038,7 @@
       <c r="B183" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C183" s="5">
+      <c r="C183" s="4">
         <v>46198</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -6028,7 +6067,7 @@
       <c r="B184" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C184" s="5">
+      <c r="C184" s="4">
         <v>46199</v>
       </c>
       <c r="D184" s="1" t="s">
@@ -6057,7 +6096,7 @@
       <c r="B185" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C185" s="5">
+      <c r="C185" s="4">
         <v>46205</v>
       </c>
       <c r="D185" s="1" t="s">
@@ -6086,7 +6125,7 @@
       <c r="B186" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C186" s="5">
+      <c r="C186" s="4">
         <v>46209</v>
       </c>
       <c r="D186" s="1" t="s">
@@ -6115,7 +6154,7 @@
       <c r="B187" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C187" s="5">
+      <c r="C187" s="4">
         <v>46209</v>
       </c>
       <c r="D187" s="1" t="s">
@@ -6144,7 +6183,7 @@
       <c r="B188" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C188" s="5">
+      <c r="C188" s="4">
         <v>46210</v>
       </c>
       <c r="D188" s="1" t="s">
@@ -6173,7 +6212,7 @@
       <c r="B189" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C189" s="5">
+      <c r="C189" s="4">
         <v>46210</v>
       </c>
       <c r="D189" s="1" t="s">
@@ -6202,7 +6241,7 @@
       <c r="B190" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C190" s="5">
+      <c r="C190" s="4">
         <v>46210</v>
       </c>
       <c r="D190" s="1" t="s">
@@ -6231,7 +6270,7 @@
       <c r="B191" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C191" s="5">
+      <c r="C191" s="4">
         <v>46212</v>
       </c>
       <c r="D191" s="1" t="s">
@@ -6260,7 +6299,7 @@
       <c r="B192" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C192" s="5">
+      <c r="C192" s="4">
         <v>46212</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -6289,7 +6328,7 @@
       <c r="B193" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C193" s="5">
+      <c r="C193" s="4">
         <v>46212</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -6318,7 +6357,7 @@
       <c r="B194" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C194" s="5">
+      <c r="C194" s="4">
         <v>46212</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -6347,7 +6386,7 @@
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C195" s="5">
+      <c r="C195" s="4">
         <v>46212</v>
       </c>
       <c r="D195" s="1" t="s">
@@ -6376,7 +6415,7 @@
       <c r="B196" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C196" s="5">
+      <c r="C196" s="4">
         <v>46213</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -6405,7 +6444,7 @@
       <c r="B197" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C197" s="5">
+      <c r="C197" s="4">
         <v>46218</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -6434,7 +6473,7 @@
       <c r="B198" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C198" s="5">
+      <c r="C198" s="4">
         <v>46216</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -6463,7 +6502,7 @@
       <c r="B199" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="5">
+      <c r="C199" s="4">
         <v>46216</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -6492,7 +6531,7 @@
       <c r="B200" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C200" s="5">
+      <c r="C200" s="4">
         <v>46219</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -6521,7 +6560,7 @@
       <c r="B201" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C201" s="5">
+      <c r="C201" s="4">
         <v>46216</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -6550,7 +6589,7 @@
       <c r="B202" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C202" s="5">
+      <c r="C202" s="4">
         <v>46217</v>
       </c>
       <c r="D202" s="1" t="s">
@@ -6579,7 +6618,7 @@
       <c r="B203" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C203" s="5">
+      <c r="C203" s="4">
         <v>46219</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -6608,7 +6647,7 @@
       <c r="B204" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C204" s="5">
+      <c r="C204" s="4">
         <v>46216</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -6637,7 +6676,7 @@
       <c r="B205" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C205" s="5">
+      <c r="C205" s="4">
         <v>46218</v>
       </c>
       <c r="D205" s="1" t="s">
@@ -6666,7 +6705,7 @@
       <c r="B206" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C206" s="5">
+      <c r="C206" s="4">
         <v>46218</v>
       </c>
       <c r="D206" s="1" t="s">
@@ -6695,7 +6734,7 @@
       <c r="B207" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="5">
+      <c r="C207" s="4">
         <v>46218</v>
       </c>
       <c r="D207" s="1" t="s">
@@ -6724,7 +6763,7 @@
       <c r="B208" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C208" s="5">
+      <c r="C208" s="4">
         <v>46216</v>
       </c>
       <c r="D208" s="1" t="s">
@@ -6753,7 +6792,7 @@
       <c r="B209" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C209" s="5">
+      <c r="C209" s="4">
         <v>46216</v>
       </c>
       <c r="D209" s="1" t="s">
@@ -6782,7 +6821,7 @@
       <c r="B210" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C210" s="5">
+      <c r="C210" s="4">
         <v>46220</v>
       </c>
       <c r="D210" s="1" t="s">
@@ -6811,7 +6850,7 @@
       <c r="B211" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C211" s="5">
+      <c r="C211" s="4">
         <v>46220</v>
       </c>
       <c r="D211" s="1" t="s">
@@ -6840,7 +6879,7 @@
       <c r="B212" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C212" s="5">
+      <c r="C212" s="4">
         <v>46219</v>
       </c>
       <c r="D212" s="1" t="s">
@@ -6869,7 +6908,7 @@
       <c r="B213" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C213" s="5">
+      <c r="C213" s="4">
         <v>46220</v>
       </c>
       <c r="D213" s="1" t="s">
@@ -6898,7 +6937,7 @@
       <c r="B214" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C214" s="5">
+      <c r="C214" s="4">
         <v>46220</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -6927,7 +6966,7 @@
       <c r="B215" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C215" s="5">
+      <c r="C215" s="4">
         <v>46223</v>
       </c>
       <c r="D215" s="1" t="s">
@@ -6956,7 +6995,7 @@
       <c r="B216" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C216" s="5">
+      <c r="C216" s="4">
         <v>46226</v>
       </c>
       <c r="D216" s="1" t="s">
@@ -6985,7 +7024,7 @@
       <c r="B217" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C217" s="5">
+      <c r="C217" s="4">
         <v>46223</v>
       </c>
       <c r="D217" s="1" t="s">
@@ -7014,7 +7053,7 @@
       <c r="B218" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C218" s="5">
+      <c r="C218" s="4">
         <v>46225</v>
       </c>
       <c r="D218" s="1" t="s">
@@ -7043,7 +7082,7 @@
       <c r="B219" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C219" s="5">
+      <c r="C219" s="4">
         <v>46225</v>
       </c>
       <c r="D219" s="1" t="s">
@@ -7072,7 +7111,7 @@
       <c r="B220" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C220" s="5">
+      <c r="C220" s="4">
         <v>46225</v>
       </c>
       <c r="D220" s="1" t="s">
@@ -7101,7 +7140,7 @@
       <c r="B221" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C221" s="5">
+      <c r="C221" s="4">
         <v>46224</v>
       </c>
       <c r="D221" s="1" t="s">
@@ -7130,7 +7169,7 @@
       <c r="B222" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C222" s="5">
+      <c r="C222" s="4">
         <v>46225</v>
       </c>
       <c r="D222" s="1" t="s">
@@ -7159,7 +7198,7 @@
       <c r="B223" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C223" s="5">
+      <c r="C223" s="4">
         <v>46227</v>
       </c>
       <c r="D223" s="1" t="s">
@@ -7188,7 +7227,7 @@
       <c r="B224" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C224" s="5">
+      <c r="C224" s="4">
         <v>46227</v>
       </c>
       <c r="D224" s="1" t="s">
@@ -7217,7 +7256,7 @@
       <c r="B225" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C225" s="5">
+      <c r="C225" s="4">
         <v>46227</v>
       </c>
       <c r="D225" s="1" t="s">
@@ -7246,7 +7285,7 @@
       <c r="B226" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C226" s="5">
+      <c r="C226" s="4">
         <v>46218</v>
       </c>
       <c r="D226" s="1" t="s">
@@ -7275,7 +7314,7 @@
       <c r="B227" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C227" s="5">
+      <c r="C227" s="4">
         <v>46224</v>
       </c>
       <c r="D227" s="1" t="s">
@@ -7304,7 +7343,7 @@
       <c r="B228" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C228" s="5">
+      <c r="C228" s="4">
         <v>46212</v>
       </c>
       <c r="D228" s="1" t="s">
@@ -7333,7 +7372,7 @@
       <c r="B229" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C229" s="5">
+      <c r="C229" s="4">
         <v>46216</v>
       </c>
       <c r="D229" s="1" t="s">
@@ -7362,7 +7401,7 @@
       <c r="B230" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C230" s="5">
+      <c r="C230" s="4">
         <v>46225</v>
       </c>
       <c r="D230" s="1" t="s">
@@ -7391,7 +7430,7 @@
       <c r="B231" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C231" s="5">
+      <c r="C231" s="4">
         <v>46224</v>
       </c>
       <c r="D231" s="1" t="s">
@@ -7420,7 +7459,7 @@
       <c r="B232" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C232" s="5">
+      <c r="C232" s="4">
         <v>46225</v>
       </c>
       <c r="D232" s="1" t="s">
@@ -7449,7 +7488,7 @@
       <c r="B233" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C233" s="5">
+      <c r="C233" s="4">
         <v>46226</v>
       </c>
       <c r="D233" s="1" t="s">
@@ -7478,7 +7517,7 @@
       <c r="B234" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C234" s="5">
+      <c r="C234" s="4">
         <v>46225</v>
       </c>
       <c r="D234" s="1" t="s">
@@ -7507,7 +7546,7 @@
       <c r="B235" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C235" s="5">
+      <c r="C235" s="4">
         <v>46230</v>
       </c>
       <c r="D235" s="1" t="s">
@@ -7536,7 +7575,7 @@
       <c r="B236" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C236" s="5">
+      <c r="C236" s="4">
         <v>46224</v>
       </c>
       <c r="D236" s="1" t="s">
@@ -7565,7 +7604,7 @@
       <c r="B237" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C237" s="5">
+      <c r="C237" s="4">
         <v>46217</v>
       </c>
       <c r="D237" s="1" t="s">
@@ -7594,7 +7633,7 @@
       <c r="B238" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C238" s="5">
+      <c r="C238" s="4">
         <v>46226</v>
       </c>
       <c r="D238" s="1" t="s">
@@ -7623,7 +7662,7 @@
       <c r="B239" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C239" s="5">
+      <c r="C239" s="4">
         <v>46231</v>
       </c>
       <c r="D239" s="1" t="s">
@@ -7652,7 +7691,7 @@
       <c r="B240" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="5">
+      <c r="C240" s="4">
         <v>46226</v>
       </c>
       <c r="D240" s="1" t="s">
@@ -7681,7 +7720,7 @@
       <c r="B241" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C241" s="5">
+      <c r="C241" s="4">
         <v>46225</v>
       </c>
       <c r="D241" s="1" t="s">
@@ -7710,7 +7749,7 @@
       <c r="B242" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C242" s="5">
+      <c r="C242" s="4">
         <v>46216</v>
       </c>
       <c r="D242" s="1" t="s">
@@ -7739,7 +7778,7 @@
       <c r="B243" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C243" s="5">
+      <c r="C243" s="4">
         <v>46223</v>
       </c>
       <c r="D243" s="1" t="s">
@@ -7768,7 +7807,7 @@
       <c r="B244" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C244" s="5">
+      <c r="C244" s="4">
         <v>46230</v>
       </c>
       <c r="D244" s="1" t="s">
@@ -7797,7 +7836,7 @@
       <c r="B245" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C245" s="5">
+      <c r="C245" s="4">
         <v>46234</v>
       </c>
       <c r="D245" s="1" t="s">
@@ -7826,7 +7865,7 @@
       <c r="B246" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C246" s="5">
+      <c r="C246" s="4">
         <v>46233</v>
       </c>
       <c r="D246" s="1" t="s">
@@ -7855,7 +7894,7 @@
       <c r="B247" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C247" s="5">
+      <c r="C247" s="4">
         <v>46233</v>
       </c>
       <c r="D247" s="1" t="s">
@@ -7884,7 +7923,7 @@
       <c r="B248" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C248" s="5">
+      <c r="C248" s="4">
         <v>46234</v>
       </c>
       <c r="D248" s="1" t="s">
@@ -7913,7 +7952,7 @@
       <c r="B249" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C249" s="5">
+      <c r="C249" s="4">
         <v>46233</v>
       </c>
       <c r="D249" s="1" t="s">
@@ -7942,7 +7981,7 @@
       <c r="B250" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C250" s="5">
+      <c r="C250" s="4">
         <v>46234</v>
       </c>
       <c r="D250" s="1" t="s">
@@ -7971,7 +8010,7 @@
       <c r="B251" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="5">
+      <c r="C251" s="4">
         <v>46233</v>
       </c>
       <c r="D251" s="1" t="s">
@@ -8000,7 +8039,7 @@
       <c r="B252" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C252" s="5">
+      <c r="C252" s="4">
         <v>46240</v>
       </c>
       <c r="D252" s="1" t="s">
@@ -8029,7 +8068,7 @@
       <c r="B253" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C253" s="5">
+      <c r="C253" s="4">
         <v>46240</v>
       </c>
       <c r="D253" s="1" t="s">
@@ -8058,7 +8097,7 @@
       <c r="B254" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C254" s="5">
+      <c r="C254" s="4">
         <v>46240</v>
       </c>
       <c r="D254" s="1" t="s">
@@ -8087,7 +8126,7 @@
       <c r="B255" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C255" s="5">
+      <c r="C255" s="4">
         <v>46239</v>
       </c>
       <c r="D255" s="1" t="s">
@@ -8116,7 +8155,7 @@
       <c r="B256" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C256" s="5">
+      <c r="C256" s="4">
         <v>46240</v>
       </c>
       <c r="D256" s="1" t="s">
@@ -8145,7 +8184,7 @@
       <c r="B257" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C257" s="5">
+      <c r="C257" s="4">
         <v>46239</v>
       </c>
       <c r="D257" s="1" t="s">
@@ -8174,7 +8213,7 @@
       <c r="B258" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C258" s="5">
+      <c r="C258" s="4">
         <v>46240</v>
       </c>
       <c r="D258" s="1" t="s">
@@ -8203,7 +8242,7 @@
       <c r="B259" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C259" s="5">
+      <c r="C259" s="4">
         <v>46239</v>
       </c>
       <c r="D259" s="1" t="s">
@@ -8232,7 +8271,7 @@
       <c r="B260" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C260" s="5">
+      <c r="C260" s="4">
         <v>46241</v>
       </c>
       <c r="D260" s="1" t="s">
@@ -8261,7 +8300,7 @@
       <c r="B261" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C261" s="5">
+      <c r="C261" s="4">
         <v>46240</v>
       </c>
       <c r="D261" s="1" t="s">
@@ -8290,7 +8329,7 @@
       <c r="B262" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="5">
+      <c r="C262" s="4">
         <v>46238</v>
       </c>
       <c r="D262" s="1" t="s">
@@ -8319,7 +8358,7 @@
       <c r="B263" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C263" s="5">
+      <c r="C263" s="4">
         <v>46238</v>
       </c>
       <c r="D263" s="1" t="s">
@@ -8348,7 +8387,7 @@
       <c r="B264" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C264" s="5">
+      <c r="C264" s="4">
         <v>46216</v>
       </c>
       <c r="D264" s="1" t="s">
@@ -8377,7 +8416,7 @@
       <c r="B265" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C265" s="5">
+      <c r="C265" s="4">
         <v>46225</v>
       </c>
       <c r="D265" s="1" t="s">
@@ -8406,7 +8445,7 @@
       <c r="B266" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C266" s="5">
+      <c r="C266" s="4">
         <v>46230</v>
       </c>
       <c r="D266" s="1" t="s">
@@ -8435,7 +8474,7 @@
       <c r="B267" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C267" s="5">
+      <c r="C267" s="4">
         <v>46217</v>
       </c>
       <c r="D267" s="1" t="s">
@@ -8464,7 +8503,7 @@
       <c r="B268" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C268" s="5">
+      <c r="C268" s="4">
         <v>46219</v>
       </c>
       <c r="D268" s="1" t="s">
@@ -8493,7 +8532,7 @@
       <c r="B269" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C269" s="5">
+      <c r="C269" s="4">
         <v>46227</v>
       </c>
       <c r="D269" s="1" t="s">
@@ -8522,7 +8561,7 @@
       <c r="B270" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C270" s="5">
+      <c r="C270" s="4">
         <v>46244</v>
       </c>
       <c r="D270" s="1" t="s">
@@ -8551,7 +8590,7 @@
       <c r="B271" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C271" s="5">
+      <c r="C271" s="4">
         <v>46246</v>
       </c>
       <c r="D271" s="1" t="s">
@@ -8580,7 +8619,7 @@
       <c r="B272" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C272" s="5">
+      <c r="C272" s="4">
         <v>46244</v>
       </c>
       <c r="D272" s="1" t="s">
@@ -8609,7 +8648,7 @@
       <c r="B273" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C273" s="5">
+      <c r="C273" s="4">
         <v>46246</v>
       </c>
       <c r="D273" s="1" t="s">
@@ -8638,7 +8677,7 @@
       <c r="B274" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C274" s="5">
+      <c r="C274" s="4">
         <v>46244</v>
       </c>
       <c r="D274" s="1" t="s">
@@ -8667,7 +8706,7 @@
       <c r="B275" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C275" s="5">
+      <c r="C275" s="4">
         <v>46247</v>
       </c>
       <c r="D275" s="1" t="s">
@@ -8696,7 +8735,7 @@
       <c r="B276" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C276" s="5">
+      <c r="C276" s="4">
         <v>46244</v>
       </c>
       <c r="D276" s="1" t="s">
@@ -8725,7 +8764,7 @@
       <c r="B277" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C277" s="5">
+      <c r="C277" s="4">
         <v>46246</v>
       </c>
       <c r="D277" s="1" t="s">
@@ -8754,7 +8793,7 @@
       <c r="B278" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C278" s="5">
+      <c r="C278" s="4">
         <v>46244</v>
       </c>
       <c r="D278" s="1" t="s">
@@ -8783,7 +8822,7 @@
       <c r="B279" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C279" s="5">
+      <c r="C279" s="4">
         <v>46246</v>
       </c>
       <c r="D279" s="1" t="s">
@@ -8812,7 +8851,7 @@
       <c r="B280" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C280" s="5">
+      <c r="C280" s="4">
         <v>46244</v>
       </c>
       <c r="D280" s="1" t="s">
@@ -8841,7 +8880,7 @@
       <c r="B281" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C281" s="5">
+      <c r="C281" s="4">
         <v>46246</v>
       </c>
       <c r="D281" s="1" t="s">
@@ -8870,7 +8909,7 @@
       <c r="B282" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C282" s="5">
+      <c r="C282" s="4">
         <v>46247</v>
       </c>
       <c r="D282" s="1" t="s">
@@ -8899,7 +8938,7 @@
       <c r="B283" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C283" s="5">
+      <c r="C283" s="4">
         <v>46245</v>
       </c>
       <c r="D283" s="1" t="s">
@@ -8928,7 +8967,7 @@
       <c r="B284" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="5">
+      <c r="C284" s="4">
         <v>46245</v>
       </c>
       <c r="D284" s="1" t="s">
@@ -8957,7 +8996,7 @@
       <c r="B285" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C285" s="5">
+      <c r="C285" s="4">
         <v>46246</v>
       </c>
       <c r="D285" s="1" t="s">
@@ -8986,7 +9025,7 @@
       <c r="B286" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C286" s="5">
+      <c r="C286" s="4">
         <v>46245</v>
       </c>
       <c r="D286" s="1" t="s">
@@ -9015,7 +9054,7 @@
       <c r="B287" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C287" s="5">
+      <c r="C287" s="4">
         <v>46245</v>
       </c>
       <c r="D287" s="1" t="s">
@@ -9044,7 +9083,7 @@
       <c r="B288" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C288" s="5">
+      <c r="C288" s="4">
         <v>46245</v>
       </c>
       <c r="D288" s="1" t="s">
@@ -9073,7 +9112,7 @@
       <c r="B289" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C289" s="5">
+      <c r="C289" s="4">
         <v>46245</v>
       </c>
       <c r="D289" s="1" t="s">
@@ -9102,7 +9141,7 @@
       <c r="B290" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C290" s="5">
+      <c r="C290" s="4">
         <v>46245</v>
       </c>
       <c r="D290" s="1" t="s">
@@ -9131,7 +9170,7 @@
       <c r="B291" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C291" s="5">
+      <c r="C291" s="4">
         <v>46244</v>
       </c>
       <c r="D291" s="1" t="s">
@@ -9160,7 +9199,7 @@
       <c r="B292" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C292" s="5">
+      <c r="C292" s="4">
         <v>46248</v>
       </c>
       <c r="D292" s="1" t="s">
@@ -9189,7 +9228,7 @@
       <c r="B293" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C293" s="5">
+      <c r="C293" s="4">
         <v>46247</v>
       </c>
       <c r="D293" s="1" t="s">
@@ -9218,7 +9257,7 @@
       <c r="B294" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C294" s="5">
+      <c r="C294" s="4">
         <v>46251</v>
       </c>
       <c r="D294" s="1" t="s">
@@ -9247,7 +9286,7 @@
       <c r="B295" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="5">
+      <c r="C295" s="4">
         <v>46252</v>
       </c>
       <c r="D295" s="1" t="s">
@@ -9276,7 +9315,7 @@
       <c r="B296" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C296" s="5">
+      <c r="C296" s="4">
         <v>46252</v>
       </c>
       <c r="D296" s="1" t="s">
@@ -9305,7 +9344,7 @@
       <c r="B297" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C297" s="5">
+      <c r="C297" s="4">
         <v>46252</v>
       </c>
       <c r="D297" s="1" t="s">
@@ -9334,7 +9373,7 @@
       <c r="B298" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C298" s="5">
+      <c r="C298" s="4">
         <v>46251</v>
       </c>
       <c r="D298" s="1" t="s">
@@ -9363,7 +9402,7 @@
       <c r="B299" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C299" s="5">
+      <c r="C299" s="4">
         <v>46251</v>
       </c>
       <c r="D299" s="1" t="s">
@@ -9392,7 +9431,7 @@
       <c r="B300" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C300" s="5">
+      <c r="C300" s="4">
         <v>46252</v>
       </c>
       <c r="D300" s="1" t="s">
@@ -9421,7 +9460,7 @@
       <c r="B301" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C301" s="5">
+      <c r="C301" s="4">
         <v>46254</v>
       </c>
       <c r="D301" s="1" t="s">
@@ -9450,7 +9489,7 @@
       <c r="B302" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C302" s="5">
+      <c r="C302" s="4">
         <v>46251</v>
       </c>
       <c r="D302" s="1" t="s">
@@ -9479,7 +9518,7 @@
       <c r="B303" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C303" s="5">
+      <c r="C303" s="4">
         <v>46253</v>
       </c>
       <c r="D303" s="1" t="s">
@@ -9508,7 +9547,7 @@
       <c r="B304" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C304" s="5">
+      <c r="C304" s="4">
         <v>46253</v>
       </c>
       <c r="D304" s="1" t="s">
@@ -9537,7 +9576,7 @@
       <c r="B305" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C305" s="5">
+      <c r="C305" s="4">
         <v>46252</v>
       </c>
       <c r="D305" s="1" t="s">
@@ -9566,7 +9605,7 @@
       <c r="B306" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C306" s="5">
+      <c r="C306" s="4">
         <v>46251</v>
       </c>
       <c r="D306" s="1" t="s">
@@ -9595,7 +9634,7 @@
       <c r="B307" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C307" s="5">
+      <c r="C307" s="4">
         <v>46251</v>
       </c>
       <c r="D307" s="1" t="s">
@@ -9624,7 +9663,7 @@
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C308" s="5">
+      <c r="C308" s="4">
         <v>46251</v>
       </c>
       <c r="D308" s="1" t="s">
@@ -9653,7 +9692,7 @@
       <c r="B309" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C309" s="5">
+      <c r="C309" s="4">
         <v>46253</v>
       </c>
       <c r="D309" s="1" t="s">
@@ -9682,7 +9721,7 @@
       <c r="B310" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C310" s="5">
+      <c r="C310" s="4">
         <v>46251</v>
       </c>
       <c r="D310" s="1" t="s">
@@ -9711,7 +9750,7 @@
       <c r="B311" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C311" s="5">
+      <c r="C311" s="4">
         <v>46252</v>
       </c>
       <c r="D311" s="1" t="s">
@@ -9740,7 +9779,7 @@
       <c r="B312" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C312" s="5">
+      <c r="C312" s="4">
         <v>46254</v>
       </c>
       <c r="D312" s="1" t="s">
@@ -9769,7 +9808,7 @@
       <c r="B313" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C313" s="5">
+      <c r="C313" s="4">
         <v>46255</v>
       </c>
       <c r="D313" s="1" t="s">
@@ -9798,7 +9837,7 @@
       <c r="B314" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C314" s="5">
+      <c r="C314" s="4">
         <v>46255</v>
       </c>
       <c r="D314" s="1" t="s">
@@ -9827,7 +9866,7 @@
       <c r="B315" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C315" s="5">
+      <c r="C315" s="4">
         <v>46255</v>
       </c>
       <c r="D315" s="1" t="s">
@@ -9856,7 +9895,7 @@
       <c r="B316" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C316" s="5">
+      <c r="C316" s="4">
         <v>46255</v>
       </c>
       <c r="D316" s="1" t="s">
@@ -9885,7 +9924,7 @@
       <c r="B317" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C317" s="5">
+      <c r="C317" s="4">
         <v>46258</v>
       </c>
       <c r="D317" s="1" t="s">
@@ -9914,7 +9953,7 @@
       <c r="B318" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C318" s="5">
+      <c r="C318" s="4">
         <v>46258</v>
       </c>
       <c r="D318" s="1" t="s">
@@ -9943,7 +9982,7 @@
       <c r="B319" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C319" s="5">
+      <c r="C319" s="4">
         <v>46261</v>
       </c>
       <c r="D319" s="1" t="s">
@@ -9972,7 +10011,7 @@
       <c r="B320" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C320" s="5">
+      <c r="C320" s="4">
         <v>46258</v>
       </c>
       <c r="D320" s="1" t="s">
@@ -10001,7 +10040,7 @@
       <c r="B321" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C321" s="5">
+      <c r="C321" s="4">
         <v>46260</v>
       </c>
       <c r="D321" s="1" t="s">
@@ -10030,7 +10069,7 @@
       <c r="B322" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C322" s="5">
+      <c r="C322" s="4">
         <v>46262</v>
       </c>
       <c r="D322" s="1" t="s">
@@ -10059,7 +10098,7 @@
       <c r="B323" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C323" s="5">
+      <c r="C323" s="4">
         <v>46262</v>
       </c>
       <c r="D323" s="1" t="s">
@@ -10088,7 +10127,7 @@
       <c r="B324" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C324" s="5">
+      <c r="C324" s="4">
         <v>46262</v>
       </c>
       <c r="D324" s="1" t="s">
@@ -10117,7 +10156,7 @@
       <c r="B325" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C325" s="5">
+      <c r="C325" s="4">
         <v>46262</v>
       </c>
       <c r="D325" s="1" t="s">
@@ -10146,7 +10185,7 @@
       <c r="B326" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C326" s="5">
+      <c r="C326" s="4">
         <v>46261</v>
       </c>
       <c r="D326" s="1" t="s">
@@ -10175,7 +10214,7 @@
       <c r="B327" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C327" s="5">
+      <c r="C327" s="4">
         <v>46268</v>
       </c>
       <c r="D327" s="1" t="s">
@@ -10204,7 +10243,7 @@
       <c r="B328" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C328" s="5">
+      <c r="C328" s="4">
         <v>46268</v>
       </c>
       <c r="D328" s="1" t="s">
@@ -10233,7 +10272,7 @@
       <c r="B329" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C329" s="5">
+      <c r="C329" s="4">
         <v>46267</v>
       </c>
       <c r="D329" s="1" t="s">
@@ -10262,7 +10301,7 @@
       <c r="B330" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C330" s="5">
+      <c r="C330" s="4">
         <v>46267</v>
       </c>
       <c r="D330" s="1" t="s">
@@ -10291,7 +10330,7 @@
       <c r="B331" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C331" s="5">
+      <c r="C331" s="4">
         <v>46268</v>
       </c>
       <c r="D331" s="1" t="s">
@@ -10320,7 +10359,7 @@
       <c r="B332" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C332" s="5">
+      <c r="C332" s="4">
         <v>46268</v>
       </c>
       <c r="D332" s="1" t="s">
@@ -10349,7 +10388,7 @@
       <c r="B333" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C333" s="5">
+      <c r="C333" s="4">
         <v>46267</v>
       </c>
       <c r="D333" s="1" t="s">
@@ -10378,7 +10417,7 @@
       <c r="B334" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C334" s="5">
+      <c r="C334" s="4">
         <v>46266</v>
       </c>
       <c r="D334" s="1" t="s">
@@ -10390,7 +10429,7 @@
       <c r="F334" s="1">
         <v>95</v>
       </c>
-      <c r="G334" s="6">
+      <c r="G334" s="2">
         <v>0.95</v>
       </c>
       <c r="H334" s="1" t="s">
@@ -10407,7 +10446,7 @@
       <c r="B335" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C335" s="5">
+      <c r="C335" s="4">
         <v>46274</v>
       </c>
       <c r="D335" s="1" t="s">
@@ -10419,7 +10458,7 @@
       <c r="F335" s="1">
         <v>100</v>
       </c>
-      <c r="G335" s="6">
+      <c r="G335" s="2">
         <v>1</v>
       </c>
       <c r="H335" s="1" t="s">
@@ -10436,7 +10475,7 @@
       <c r="B336" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C336" s="5">
+      <c r="C336" s="4">
         <v>46266</v>
       </c>
       <c r="D336" s="1" t="s">
@@ -10448,7 +10487,7 @@
       <c r="F336" s="1">
         <v>100</v>
       </c>
-      <c r="G336" s="6">
+      <c r="G336" s="2">
         <v>1</v>
       </c>
       <c r="H336" s="1" t="s">
@@ -10465,7 +10504,7 @@
       <c r="B337" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C337" s="5">
+      <c r="C337" s="4">
         <v>46275</v>
       </c>
       <c r="D337" s="1" t="s">
@@ -10477,7 +10516,7 @@
       <c r="F337" s="1">
         <v>95</v>
       </c>
-      <c r="G337" s="6">
+      <c r="G337" s="2">
         <v>0.95</v>
       </c>
       <c r="H337" s="1" t="s">
@@ -10494,7 +10533,7 @@
       <c r="B338" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C338" s="5">
+      <c r="C338" s="4">
         <v>46274</v>
       </c>
       <c r="D338" s="1" t="s">
@@ -10506,7 +10545,7 @@
       <c r="F338" s="1">
         <v>95</v>
       </c>
-      <c r="G338" s="6">
+      <c r="G338" s="2">
         <v>0.95</v>
       </c>
       <c r="H338" s="1" t="s">
@@ -10523,7 +10562,7 @@
       <c r="B339" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C339" s="5">
+      <c r="C339" s="4">
         <v>46275</v>
       </c>
       <c r="D339" s="1" t="s">
@@ -10535,7 +10574,7 @@
       <c r="F339" s="1">
         <v>100</v>
       </c>
-      <c r="G339" s="6">
+      <c r="G339" s="2">
         <v>1</v>
       </c>
       <c r="H339" s="1" t="s">
@@ -10552,7 +10591,7 @@
       <c r="B340" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C340" s="5">
+      <c r="C340" s="4">
         <v>46273</v>
       </c>
       <c r="D340" s="1" t="s">
@@ -10564,7 +10603,7 @@
       <c r="F340" s="1">
         <v>95</v>
       </c>
-      <c r="G340" s="6">
+      <c r="G340" s="2">
         <v>0.95</v>
       </c>
       <c r="H340" s="1" t="s">
@@ -10581,7 +10620,7 @@
       <c r="B341" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C341" s="5">
+      <c r="C341" s="4">
         <v>46273</v>
       </c>
       <c r="D341" s="1" t="s">
@@ -10593,7 +10632,7 @@
       <c r="F341" s="1">
         <v>100</v>
       </c>
-      <c r="G341" s="6">
+      <c r="G341" s="2">
         <v>1</v>
       </c>
       <c r="H341" s="1" t="s">
@@ -10610,7 +10649,7 @@
       <c r="B342" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C342" s="5">
+      <c r="C342" s="4">
         <v>46274</v>
       </c>
       <c r="D342" s="1" t="s">
@@ -10622,7 +10661,7 @@
       <c r="F342" s="1">
         <v>85</v>
       </c>
-      <c r="G342" s="6">
+      <c r="G342" s="2">
         <v>0.85</v>
       </c>
       <c r="H342" s="1" t="s">
@@ -10639,7 +10678,7 @@
       <c r="B343" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C343" s="5">
+      <c r="C343" s="4">
         <v>46273</v>
       </c>
       <c r="D343" s="1" t="s">
@@ -10651,7 +10690,7 @@
       <c r="F343" s="1">
         <v>100</v>
       </c>
-      <c r="G343" s="6">
+      <c r="G343" s="2">
         <v>1</v>
       </c>
       <c r="H343" s="1" t="s">
@@ -10668,7 +10707,7 @@
       <c r="B344" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C344" s="5">
+      <c r="C344" s="4">
         <v>46273</v>
       </c>
       <c r="D344" s="1" t="s">
@@ -10680,7 +10719,7 @@
       <c r="F344" s="1">
         <v>95</v>
       </c>
-      <c r="G344" s="6">
+      <c r="G344" s="2">
         <v>0.95</v>
       </c>
       <c r="H344" s="1" t="s">
@@ -10697,7 +10736,7 @@
       <c r="B345" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C345" s="5">
+      <c r="C345" s="4">
         <v>46275</v>
       </c>
       <c r="D345" s="1" t="s">
@@ -10709,7 +10748,7 @@
       <c r="F345" s="1">
         <v>100</v>
       </c>
-      <c r="G345" s="6">
+      <c r="G345" s="2">
         <v>1</v>
       </c>
       <c r="H345" s="1" t="s">
@@ -10726,7 +10765,7 @@
       <c r="B346" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C346" s="5">
+      <c r="C346" s="4">
         <v>46275</v>
       </c>
       <c r="D346" s="1" t="s">
@@ -10738,7 +10777,7 @@
       <c r="F346" s="1">
         <v>100</v>
       </c>
-      <c r="G346" s="6">
+      <c r="G346" s="2">
         <v>1</v>
       </c>
       <c r="H346" s="1" t="s">
@@ -10755,7 +10794,7 @@
       <c r="B347" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C347" s="5">
+      <c r="C347" s="4">
         <v>46273</v>
       </c>
       <c r="D347" s="1" t="s">
@@ -10767,7 +10806,7 @@
       <c r="F347" s="1">
         <v>90</v>
       </c>
-      <c r="G347" s="6">
+      <c r="G347" s="2">
         <v>0.9</v>
       </c>
       <c r="H347" s="1" t="s">
@@ -10784,7 +10823,7 @@
       <c r="B348" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C348" s="5">
+      <c r="C348" s="4">
         <v>46276</v>
       </c>
       <c r="D348" s="1" t="s">
@@ -10796,7 +10835,7 @@
       <c r="F348" s="1">
         <v>100</v>
       </c>
-      <c r="G348" s="6">
+      <c r="G348" s="2">
         <v>1</v>
       </c>
       <c r="H348" s="1" t="s">
@@ -10813,7 +10852,7 @@
       <c r="B349" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C349" s="5">
+      <c r="C349" s="4">
         <v>46275</v>
       </c>
       <c r="D349" s="1" t="s">
@@ -10825,7 +10864,7 @@
       <c r="F349" s="1">
         <v>95</v>
       </c>
-      <c r="G349" s="6">
+      <c r="G349" s="2">
         <v>0.95</v>
       </c>
       <c r="H349" s="1" t="s">
@@ -10842,7 +10881,7 @@
       <c r="B350" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C350" s="5">
+      <c r="C350" s="4">
         <v>46274</v>
       </c>
       <c r="D350" s="1" t="s">
@@ -10854,13 +10893,216 @@
       <c r="F350" s="1">
         <v>100</v>
       </c>
-      <c r="G350" s="6">
+      <c r="G350" s="2">
         <v>1</v>
       </c>
       <c r="H350" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I350" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C351" s="6">
+        <v>46275</v>
+      </c>
+      <c r="D351" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E351" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F351" s="5">
+        <v>100</v>
+      </c>
+      <c r="G351" s="7">
+        <v>1</v>
+      </c>
+      <c r="H351" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I351" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" s="6">
+        <v>46267</v>
+      </c>
+      <c r="D352" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E352" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="5">
+        <v>100</v>
+      </c>
+      <c r="G352" s="7">
+        <v>1</v>
+      </c>
+      <c r="H352" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I352" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" s="6">
+        <v>46276</v>
+      </c>
+      <c r="D353" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E353" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F353" s="5">
+        <v>100</v>
+      </c>
+      <c r="G353" s="7">
+        <v>1</v>
+      </c>
+      <c r="H353" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I353" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="6">
+        <v>46276</v>
+      </c>
+      <c r="D354" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E354" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="5">
+        <v>100</v>
+      </c>
+      <c r="G354" s="7">
+        <v>1</v>
+      </c>
+      <c r="H354" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I354" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="6">
+        <v>46276</v>
+      </c>
+      <c r="D355" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E355" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F355" s="5">
+        <v>100</v>
+      </c>
+      <c r="G355" s="7">
+        <v>1</v>
+      </c>
+      <c r="H355" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I355" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="6">
+        <v>46276</v>
+      </c>
+      <c r="D356" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F356" s="5">
+        <v>100</v>
+      </c>
+      <c r="G356" s="7">
+        <v>1</v>
+      </c>
+      <c r="H356" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I356" s="5">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="6">
+        <v>46273</v>
+      </c>
+      <c r="D357" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F357" s="5">
+        <v>100</v>
+      </c>
+      <c r="G357" s="7">
+        <v>1</v>
+      </c>
+      <c r="H357" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I357" s="5">
         <v>2026</v>
       </c>
     </row>
@@ -10885,19 +11127,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11251,15 +11493,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bbf009f58139d30e700e9d9dd8708ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bbfb5a56ff61f0f4bba1626b54b38306" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -11516,6 +11749,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11531,14 +11773,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B400D-C15B-4808-975D-D6FB017A04F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11553,6 +11787,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6AF3DD3-7B93-49F0-8884-8528CF69AE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC2FBD7-0487-49CA-8C3C-920C17CA81EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25260" yWindow="45" windowWidth="26445" windowHeight="20340" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="-45" yWindow="15" windowWidth="21525" windowHeight="20880" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1894" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -294,35 +294,27 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="3">
     <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <font>
@@ -343,37 +335,6 @@
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -388,28 +349,28 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I357" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
-  <autoFilter ref="A1:I357" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I196">
-    <sortCondition ref="C1:C196"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I376" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I376" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I373">
+    <sortCondition ref="A1:A373"/>
   </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{6551223E-2902-4D9E-887E-72F4C30CFEBB}" name="DateOfCall" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact" dataDxfId="7"/>
-    <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed" dataDxfId="6"/>
-    <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore" dataDxfId="5"/>
-    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="4" dataCellStyle="Percent"/>
-    <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth" dataDxfId="3"/>
-    <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
+    <tableColumn id="2" xr3:uid="{13759531-2D3E-4AB5-99AA-3CEAD45C9112}" name="ManagerTeam"/>
+    <tableColumn id="3" xr3:uid="{6551223E-2902-4D9E-887E-72F4C30CFEBB}" name="DateOfCall"/>
+    <tableColumn id="15" xr3:uid="{156F7529-7782-4A87-B4E7-76854F1D035A}" name="IssueResolvedFirstContact"/>
+    <tableColumn id="10" xr3:uid="{FA20FC87-A813-482F-AA10-876B721360F4}" name="CallFailed"/>
+    <tableColumn id="11" xr3:uid="{DF145C57-18CF-4D90-A45D-FAACD0306130}" name="TotalScore"/>
+    <tableColumn id="12" xr3:uid="{0876AC93-D420-4B04-9EE3-448E495D6B83}" name="Percentage" dataDxfId="1" dataCellStyle="Percent"/>
+    <tableColumn id="13" xr3:uid="{88DA4CA6-A215-4FB1-8A6D-379852A7EEFA}" name="ReviewMonth"/>
+    <tableColumn id="14" xr3:uid="{35631D79-8CE9-47C8-A757-76CCFBACC54F}" name="ReviewYear"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}" name="tblAssociateReference" displayName="tblAssociateReference" ref="A1:E21" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:E21" xr:uid="{E85CBB91-BC75-41DF-99F9-2D6020291053}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{8E0548F5-70FF-454C-A4FF-1E3FA7D9C27E}" name="AssociateName"/>
@@ -739,18 +700,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I357"/>
+  <dimension ref="A1:I376"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -789,7 +750,7 @@
       <c r="B2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>46113</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -818,7 +779,7 @@
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>46113</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -847,7 +808,7 @@
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>46113</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -876,7 +837,7 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="5">
         <v>46113</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -905,7 +866,7 @@
       <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="5">
         <v>46113</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -934,7 +895,7 @@
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7" s="5">
         <v>46114</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -963,7 +924,7 @@
       <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="5">
         <v>46114</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -992,7 +953,7 @@
       <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9" s="5">
         <v>46114</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -1021,7 +982,7 @@
       <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="5">
         <v>46118</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1050,7 +1011,7 @@
       <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="5">
         <v>46118</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1079,7 +1040,7 @@
       <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="5">
         <v>46119</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1108,7 +1069,7 @@
       <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13" s="5">
         <v>46119</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1137,7 +1098,7 @@
       <c r="B14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14" s="5">
         <v>46119</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1166,7 +1127,7 @@
       <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
         <v>46120</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1195,7 +1156,7 @@
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16" s="5">
         <v>46120</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1224,7 +1185,7 @@
       <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17" s="5">
         <v>46120</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1253,7 +1214,7 @@
       <c r="B18" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="5">
         <v>46120</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1282,7 +1243,7 @@
       <c r="B19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="5">
         <v>46121</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1311,7 +1272,7 @@
       <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="4">
+      <c r="C20" s="5">
         <v>46121</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1340,7 +1301,7 @@
       <c r="B21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="4">
+      <c r="C21" s="5">
         <v>46121</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1369,7 +1330,7 @@
       <c r="B22" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="5">
         <v>46121</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1398,7 +1359,7 @@
       <c r="B23" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="5">
         <v>46122</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -1427,7 +1388,7 @@
       <c r="B24" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="5">
         <v>46122</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1456,7 +1417,7 @@
       <c r="B25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="5">
         <v>46122</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1485,7 +1446,7 @@
       <c r="B26" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="5">
         <v>46122</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1514,7 +1475,7 @@
       <c r="B27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="5">
         <v>46125</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1543,7 +1504,7 @@
       <c r="B28" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="5">
         <v>46126</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1572,7 +1533,7 @@
       <c r="B29" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="5">
         <v>46126</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1601,7 +1562,7 @@
       <c r="B30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="5">
         <v>46126</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1630,7 +1591,7 @@
       <c r="B31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="5">
         <v>46127</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1659,7 +1620,7 @@
       <c r="B32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="5">
         <v>46127</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1688,7 +1649,7 @@
       <c r="B33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="5">
         <v>46127</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1717,7 +1678,7 @@
       <c r="B34" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="5">
         <v>46127</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -1746,7 +1707,7 @@
       <c r="B35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="5">
         <v>46128</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -1775,7 +1736,7 @@
       <c r="B36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="5">
         <v>46128</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -1804,7 +1765,7 @@
       <c r="B37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="5">
         <v>46128</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -1833,7 +1794,7 @@
       <c r="B38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="5">
         <v>46128</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -1862,7 +1823,7 @@
       <c r="B39" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="5">
         <v>46129</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -1891,7 +1852,7 @@
       <c r="B40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="5">
         <v>46129</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -1920,7 +1881,7 @@
       <c r="B41" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="5">
         <v>46129</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -1949,7 +1910,7 @@
       <c r="B42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="5">
         <v>46133</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -1978,7 +1939,7 @@
       <c r="B43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="5">
         <v>46134</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2007,7 +1968,7 @@
       <c r="B44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="5">
         <v>46134</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2036,7 +1997,7 @@
       <c r="B45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="5">
         <v>46134</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2065,7 +2026,7 @@
       <c r="B46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="5">
         <v>46135</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2094,7 +2055,7 @@
       <c r="B47" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="5">
         <v>46135</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2123,7 +2084,7 @@
       <c r="B48" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="5">
         <v>46135</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2152,7 +2113,7 @@
       <c r="B49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="5">
         <v>46135</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2181,7 +2142,7 @@
       <c r="B50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="5">
         <v>46135</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2210,7 +2171,7 @@
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="5">
         <v>46135</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2239,7 +2200,7 @@
       <c r="B52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="5">
         <v>46135</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2268,7 +2229,7 @@
       <c r="B53" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="5">
         <v>46140</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2297,7 +2258,7 @@
       <c r="B54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="5">
         <v>46140</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -2326,7 +2287,7 @@
       <c r="B55" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="5">
         <v>46141</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -2355,7 +2316,7 @@
       <c r="B56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="5">
         <v>46141</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -2384,7 +2345,7 @@
       <c r="B57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="5">
         <v>46141</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -2413,7 +2374,7 @@
       <c r="B58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="5">
         <v>46141</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -2442,7 +2403,7 @@
       <c r="B59" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="5">
         <v>46141</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2471,7 +2432,7 @@
       <c r="B60" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="5">
         <v>46142</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -2500,7 +2461,7 @@
       <c r="B61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="5">
         <v>46142</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -2529,7 +2490,7 @@
       <c r="B62" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="5">
         <v>46142</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -2558,7 +2519,7 @@
       <c r="B63" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="5">
         <v>46142</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -2587,7 +2548,7 @@
       <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="5">
         <v>46142</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -2616,7 +2577,7 @@
       <c r="B65" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="5">
         <v>46142</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -2645,7 +2606,7 @@
       <c r="B66" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="5">
         <v>46142</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -2674,7 +2635,7 @@
       <c r="B67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="5">
         <v>46143</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -2703,7 +2664,7 @@
       <c r="B68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="5">
         <v>46143</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -2732,7 +2693,7 @@
       <c r="B69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="5">
         <v>46147</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -2761,7 +2722,7 @@
       <c r="B70" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="5">
         <v>46147</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -2790,7 +2751,7 @@
       <c r="B71" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="5">
         <v>46147</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -2819,7 +2780,7 @@
       <c r="B72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="5">
         <v>46148</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -2848,7 +2809,7 @@
       <c r="B73" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="5">
         <v>46148</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -2877,7 +2838,7 @@
       <c r="B74" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="5">
         <v>46148</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -2906,7 +2867,7 @@
       <c r="B75" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="5">
         <v>46148</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -2935,7 +2896,7 @@
       <c r="B76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="5">
         <v>46149</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -2964,7 +2925,7 @@
       <c r="B77" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="5">
         <v>46149</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -2993,7 +2954,7 @@
       <c r="B78" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="5">
         <v>46149</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3022,7 +2983,7 @@
       <c r="B79" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="5">
         <v>46149</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3051,7 +3012,7 @@
       <c r="B80" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="5">
         <v>46149</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3080,7 +3041,7 @@
       <c r="B81" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="5">
         <v>46149</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3109,7 +3070,7 @@
       <c r="B82" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="5">
         <v>46149</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3138,7 +3099,7 @@
       <c r="B83" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="5">
         <v>46150</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3167,7 +3128,7 @@
       <c r="B84" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="5">
         <v>46153</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3196,7 +3157,7 @@
       <c r="B85" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="5">
         <v>46154</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3225,7 +3186,7 @@
       <c r="B86" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="5">
         <v>46154</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3254,7 +3215,7 @@
       <c r="B87" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="5">
         <v>46154</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3283,7 +3244,7 @@
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="5">
         <v>46154</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3312,7 +3273,7 @@
       <c r="B89" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="5">
         <v>46155</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3341,7 +3302,7 @@
       <c r="B90" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="5">
         <v>46155</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3370,7 +3331,7 @@
       <c r="B91" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="5">
         <v>46155</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3399,7 +3360,7 @@
       <c r="B92" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="5">
         <v>46155</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3428,7 +3389,7 @@
       <c r="B93" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="5">
         <v>46156</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3457,7 +3418,7 @@
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="5">
         <v>46156</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3486,7 +3447,7 @@
       <c r="B95" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="5">
         <v>46156</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3515,7 +3476,7 @@
       <c r="B96" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="5">
         <v>46156</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -3544,7 +3505,7 @@
       <c r="B97" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="5">
         <v>46157</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -3573,7 +3534,7 @@
       <c r="B98" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="5">
         <v>46157</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -3602,7 +3563,7 @@
       <c r="B99" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="5">
         <v>46157</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -3631,7 +3592,7 @@
       <c r="B100" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="5">
         <v>46161</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -3660,7 +3621,7 @@
       <c r="B101" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="5">
         <v>46162</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -3689,7 +3650,7 @@
       <c r="B102" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="5">
         <v>46168</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -3718,7 +3679,7 @@
       <c r="B103" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="5">
         <v>46168</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -3747,7 +3708,7 @@
       <c r="B104" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="5">
         <v>46168</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -3776,7 +3737,7 @@
       <c r="B105" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="5">
         <v>46169</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -3805,7 +3766,7 @@
       <c r="B106" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="5">
         <v>46169</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -3834,7 +3795,7 @@
       <c r="B107" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="5">
         <v>46170</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -3863,7 +3824,7 @@
       <c r="B108" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="5">
         <v>46170</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -3892,7 +3853,7 @@
       <c r="B109" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="5">
         <v>46170</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -3921,7 +3882,7 @@
       <c r="B110" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="5">
         <v>46170</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -3950,7 +3911,7 @@
       <c r="B111" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="5">
         <v>46170</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -3979,7 +3940,7 @@
       <c r="B112" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="5">
         <v>46171</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4008,7 +3969,7 @@
       <c r="B113" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C113" s="4">
+      <c r="C113" s="5">
         <v>46171</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4037,7 +3998,7 @@
       <c r="B114" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C114" s="4">
+      <c r="C114" s="5">
         <v>46171</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4066,7 +4027,7 @@
       <c r="B115" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C115" s="4">
+      <c r="C115" s="5">
         <v>46174</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -4095,7 +4056,7 @@
       <c r="B116" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C116" s="4">
+      <c r="C116" s="5">
         <v>46174</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -4124,7 +4085,7 @@
       <c r="B117" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C117" s="4">
+      <c r="C117" s="5">
         <v>46174</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -4153,7 +4114,7 @@
       <c r="B118" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C118" s="4">
+      <c r="C118" s="5">
         <v>46175</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4182,7 +4143,7 @@
       <c r="B119" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C119" s="4">
+      <c r="C119" s="5">
         <v>46175</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4211,7 +4172,7 @@
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C120" s="4">
+      <c r="C120" s="5">
         <v>46176</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4240,7 +4201,7 @@
       <c r="B121" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C121" s="4">
+      <c r="C121" s="5">
         <v>46176</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4269,7 +4230,7 @@
       <c r="B122" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C122" s="4">
+      <c r="C122" s="5">
         <v>46177</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4298,7 +4259,7 @@
       <c r="B123" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C123" s="4">
+      <c r="C123" s="5">
         <v>46178</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -4327,7 +4288,7 @@
       <c r="B124" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C124" s="4">
+      <c r="C124" s="5">
         <v>46178</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -4356,7 +4317,7 @@
       <c r="B125" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C125" s="4">
+      <c r="C125" s="5">
         <v>46178</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -4385,7 +4346,7 @@
       <c r="B126" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C126" s="4">
+      <c r="C126" s="5">
         <v>46178</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -4414,7 +4375,7 @@
       <c r="B127" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C127" s="4">
+      <c r="C127" s="5">
         <v>46178</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -4443,7 +4404,7 @@
       <c r="B128" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C128" s="4">
+      <c r="C128" s="5">
         <v>46178</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -4472,7 +4433,7 @@
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C129" s="4">
+      <c r="C129" s="5">
         <v>46181</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -4501,7 +4462,7 @@
       <c r="B130" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C130" s="4">
+      <c r="C130" s="5">
         <v>46181</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -4530,7 +4491,7 @@
       <c r="B131" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C131" s="4">
+      <c r="C131" s="5">
         <v>46181</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -4559,7 +4520,7 @@
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C132" s="4">
+      <c r="C132" s="5">
         <v>46182</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -4588,7 +4549,7 @@
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C133" s="4">
+      <c r="C133" s="5">
         <v>46182</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -4617,7 +4578,7 @@
       <c r="B134" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C134" s="4">
+      <c r="C134" s="5">
         <v>46182</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -4646,7 +4607,7 @@
       <c r="B135" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C135" s="4">
+      <c r="C135" s="5">
         <v>46182</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -4675,7 +4636,7 @@
       <c r="B136" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C136" s="4">
+      <c r="C136" s="5">
         <v>46182</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -4704,7 +4665,7 @@
       <c r="B137" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C137" s="4">
+      <c r="C137" s="5">
         <v>46182</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -4733,7 +4694,7 @@
       <c r="B138" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C138" s="4">
+      <c r="C138" s="5">
         <v>46182</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -4762,7 +4723,7 @@
       <c r="B139" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C139" s="4">
+      <c r="C139" s="5">
         <v>46182</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -4791,7 +4752,7 @@
       <c r="B140" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140" s="5">
         <v>46182</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -4820,7 +4781,7 @@
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141" s="5">
         <v>46183</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -4849,7 +4810,7 @@
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142" s="5">
         <v>46183</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -4878,7 +4839,7 @@
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143" s="5">
         <v>46184</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -4907,7 +4868,7 @@
       <c r="B144" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144" s="5">
         <v>46184</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -4936,7 +4897,7 @@
       <c r="B145" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145" s="5">
         <v>46184</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -4965,7 +4926,7 @@
       <c r="B146" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="5">
         <v>46184</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -4994,7 +4955,7 @@
       <c r="B147" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147" s="5">
         <v>46184</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -5023,7 +4984,7 @@
       <c r="B148" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148" s="5">
         <v>46184</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -5052,7 +5013,7 @@
       <c r="B149" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149" s="5">
         <v>46184</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -5081,7 +5042,7 @@
       <c r="B150" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150" s="5">
         <v>46185</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -5110,7 +5071,7 @@
       <c r="B151" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C151" s="4">
+      <c r="C151" s="5">
         <v>46185</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -5139,7 +5100,7 @@
       <c r="B152" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C152" s="4">
+      <c r="C152" s="5">
         <v>46188</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -5168,7 +5129,7 @@
       <c r="B153" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C153" s="4">
+      <c r="C153" s="5">
         <v>46188</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -5197,7 +5158,7 @@
       <c r="B154" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C154" s="4">
+      <c r="C154" s="5">
         <v>46188</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -5226,7 +5187,7 @@
       <c r="B155" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C155" s="4">
+      <c r="C155" s="5">
         <v>46188</v>
       </c>
       <c r="D155" s="1" t="s">
@@ -5255,7 +5216,7 @@
       <c r="B156" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C156" s="4">
+      <c r="C156" s="5">
         <v>46188</v>
       </c>
       <c r="D156" s="1" t="s">
@@ -5284,7 +5245,7 @@
       <c r="B157" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C157" s="4">
+      <c r="C157" s="5">
         <v>46188</v>
       </c>
       <c r="D157" s="1" t="s">
@@ -5313,7 +5274,7 @@
       <c r="B158" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C158" s="4">
+      <c r="C158" s="5">
         <v>46188</v>
       </c>
       <c r="D158" s="1" t="s">
@@ -5342,7 +5303,7 @@
       <c r="B159" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C159" s="4">
+      <c r="C159" s="5">
         <v>46188</v>
       </c>
       <c r="D159" s="1" t="s">
@@ -5371,7 +5332,7 @@
       <c r="B160" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C160" s="4">
+      <c r="C160" s="5">
         <v>46189</v>
       </c>
       <c r="D160" s="1" t="s">
@@ -5400,7 +5361,7 @@
       <c r="B161" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C161" s="4">
+      <c r="C161" s="5">
         <v>46189</v>
       </c>
       <c r="D161" s="1" t="s">
@@ -5429,7 +5390,7 @@
       <c r="B162" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C162" s="4">
+      <c r="C162" s="5">
         <v>46189</v>
       </c>
       <c r="D162" s="1" t="s">
@@ -5458,7 +5419,7 @@
       <c r="B163" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C163" s="4">
+      <c r="C163" s="5">
         <v>46189</v>
       </c>
       <c r="D163" s="1" t="s">
@@ -5487,7 +5448,7 @@
       <c r="B164" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C164" s="4">
+      <c r="C164" s="5">
         <v>46190</v>
       </c>
       <c r="D164" s="1" t="s">
@@ -5516,7 +5477,7 @@
       <c r="B165" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C165" s="4">
+      <c r="C165" s="5">
         <v>46190</v>
       </c>
       <c r="D165" s="1" t="s">
@@ -5545,7 +5506,7 @@
       <c r="B166" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C166" s="4">
+      <c r="C166" s="5">
         <v>46190</v>
       </c>
       <c r="D166" s="1" t="s">
@@ -5574,7 +5535,7 @@
       <c r="B167" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167" s="5">
         <v>46191</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -5603,7 +5564,7 @@
       <c r="B168" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168" s="5">
         <v>46191</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -5632,7 +5593,7 @@
       <c r="B169" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169" s="5">
         <v>46191</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -5661,7 +5622,7 @@
       <c r="B170" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170" s="5">
         <v>46191</v>
       </c>
       <c r="D170" s="1" t="s">
@@ -5690,7 +5651,7 @@
       <c r="B171" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171" s="5">
         <v>46191</v>
       </c>
       <c r="D171" s="1" t="s">
@@ -5719,7 +5680,7 @@
       <c r="B172" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172" s="5">
         <v>46191</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -5748,7 +5709,7 @@
       <c r="B173" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C173" s="4">
+      <c r="C173" s="5">
         <v>46195</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -5777,7 +5738,7 @@
       <c r="B174" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C174" s="4">
+      <c r="C174" s="5">
         <v>46196</v>
       </c>
       <c r="D174" s="1" t="s">
@@ -5806,7 +5767,7 @@
       <c r="B175" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C175" s="4">
+      <c r="C175" s="5">
         <v>46197</v>
       </c>
       <c r="D175" s="1" t="s">
@@ -5835,7 +5796,7 @@
       <c r="B176" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C176" s="4">
+      <c r="C176" s="5">
         <v>46197</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -5864,7 +5825,7 @@
       <c r="B177" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C177" s="4">
+      <c r="C177" s="5">
         <v>46198</v>
       </c>
       <c r="D177" s="1" t="s">
@@ -5893,7 +5854,7 @@
       <c r="B178" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C178" s="4">
+      <c r="C178" s="5">
         <v>46198</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -5922,7 +5883,7 @@
       <c r="B179" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C179" s="4">
+      <c r="C179" s="5">
         <v>46198</v>
       </c>
       <c r="D179" s="1" t="s">
@@ -5951,7 +5912,7 @@
       <c r="B180" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C180" s="4">
+      <c r="C180" s="5">
         <v>46198</v>
       </c>
       <c r="D180" s="1" t="s">
@@ -5980,7 +5941,7 @@
       <c r="B181" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C181" s="4">
+      <c r="C181" s="5">
         <v>46198</v>
       </c>
       <c r="D181" s="1" t="s">
@@ -6009,7 +5970,7 @@
       <c r="B182" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C182" s="4">
+      <c r="C182" s="5">
         <v>46198</v>
       </c>
       <c r="D182" s="1" t="s">
@@ -6038,7 +5999,7 @@
       <c r="B183" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C183" s="4">
+      <c r="C183" s="5">
         <v>46198</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -6067,7 +6028,7 @@
       <c r="B184" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C184" s="4">
+      <c r="C184" s="5">
         <v>46199</v>
       </c>
       <c r="D184" s="1" t="s">
@@ -6096,7 +6057,7 @@
       <c r="B185" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C185" s="4">
+      <c r="C185" s="5">
         <v>46205</v>
       </c>
       <c r="D185" s="1" t="s">
@@ -6125,7 +6086,7 @@
       <c r="B186" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C186" s="4">
+      <c r="C186" s="5">
         <v>46209</v>
       </c>
       <c r="D186" s="1" t="s">
@@ -6154,7 +6115,7 @@
       <c r="B187" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C187" s="4">
+      <c r="C187" s="5">
         <v>46209</v>
       </c>
       <c r="D187" s="1" t="s">
@@ -6183,7 +6144,7 @@
       <c r="B188" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C188" s="4">
+      <c r="C188" s="5">
         <v>46210</v>
       </c>
       <c r="D188" s="1" t="s">
@@ -6212,7 +6173,7 @@
       <c r="B189" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C189" s="4">
+      <c r="C189" s="5">
         <v>46210</v>
       </c>
       <c r="D189" s="1" t="s">
@@ -6241,7 +6202,7 @@
       <c r="B190" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C190" s="4">
+      <c r="C190" s="5">
         <v>46210</v>
       </c>
       <c r="D190" s="1" t="s">
@@ -6270,7 +6231,7 @@
       <c r="B191" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C191" s="4">
+      <c r="C191" s="5">
         <v>46212</v>
       </c>
       <c r="D191" s="1" t="s">
@@ -6299,7 +6260,7 @@
       <c r="B192" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C192" s="4">
+      <c r="C192" s="5">
         <v>46212</v>
       </c>
       <c r="D192" s="1" t="s">
@@ -6328,7 +6289,7 @@
       <c r="B193" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C193" s="4">
+      <c r="C193" s="5">
         <v>46212</v>
       </c>
       <c r="D193" s="1" t="s">
@@ -6357,7 +6318,7 @@
       <c r="B194" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C194" s="4">
+      <c r="C194" s="5">
         <v>46212</v>
       </c>
       <c r="D194" s="1" t="s">
@@ -6386,7 +6347,7 @@
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C195" s="4">
+      <c r="C195" s="5">
         <v>46212</v>
       </c>
       <c r="D195" s="1" t="s">
@@ -6415,7 +6376,7 @@
       <c r="B196" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C196" s="4">
+      <c r="C196" s="5">
         <v>46213</v>
       </c>
       <c r="D196" s="1" t="s">
@@ -6444,7 +6405,7 @@
       <c r="B197" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C197" s="4">
+      <c r="C197" s="5">
         <v>46218</v>
       </c>
       <c r="D197" s="1" t="s">
@@ -6473,7 +6434,7 @@
       <c r="B198" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C198" s="4">
+      <c r="C198" s="5">
         <v>46216</v>
       </c>
       <c r="D198" s="1" t="s">
@@ -6502,7 +6463,7 @@
       <c r="B199" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C199" s="4">
+      <c r="C199" s="5">
         <v>46216</v>
       </c>
       <c r="D199" s="1" t="s">
@@ -6531,7 +6492,7 @@
       <c r="B200" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C200" s="4">
+      <c r="C200" s="5">
         <v>46219</v>
       </c>
       <c r="D200" s="1" t="s">
@@ -6560,7 +6521,7 @@
       <c r="B201" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C201" s="4">
+      <c r="C201" s="5">
         <v>46216</v>
       </c>
       <c r="D201" s="1" t="s">
@@ -6589,7 +6550,7 @@
       <c r="B202" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C202" s="4">
+      <c r="C202" s="5">
         <v>46217</v>
       </c>
       <c r="D202" s="1" t="s">
@@ -6618,7 +6579,7 @@
       <c r="B203" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C203" s="4">
+      <c r="C203" s="5">
         <v>46219</v>
       </c>
       <c r="D203" s="1" t="s">
@@ -6647,7 +6608,7 @@
       <c r="B204" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C204" s="4">
+      <c r="C204" s="5">
         <v>46216</v>
       </c>
       <c r="D204" s="1" t="s">
@@ -6676,7 +6637,7 @@
       <c r="B205" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C205" s="4">
+      <c r="C205" s="5">
         <v>46218</v>
       </c>
       <c r="D205" s="1" t="s">
@@ -6705,7 +6666,7 @@
       <c r="B206" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C206" s="4">
+      <c r="C206" s="5">
         <v>46218</v>
       </c>
       <c r="D206" s="1" t="s">
@@ -6734,7 +6695,7 @@
       <c r="B207" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C207" s="4">
+      <c r="C207" s="5">
         <v>46218</v>
       </c>
       <c r="D207" s="1" t="s">
@@ -6763,7 +6724,7 @@
       <c r="B208" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C208" s="4">
+      <c r="C208" s="5">
         <v>46216</v>
       </c>
       <c r="D208" s="1" t="s">
@@ -6792,7 +6753,7 @@
       <c r="B209" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C209" s="4">
+      <c r="C209" s="5">
         <v>46216</v>
       </c>
       <c r="D209" s="1" t="s">
@@ -6821,7 +6782,7 @@
       <c r="B210" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C210" s="4">
+      <c r="C210" s="5">
         <v>46220</v>
       </c>
       <c r="D210" s="1" t="s">
@@ -6850,7 +6811,7 @@
       <c r="B211" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C211" s="4">
+      <c r="C211" s="5">
         <v>46220</v>
       </c>
       <c r="D211" s="1" t="s">
@@ -6879,7 +6840,7 @@
       <c r="B212" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C212" s="4">
+      <c r="C212" s="5">
         <v>46219</v>
       </c>
       <c r="D212" s="1" t="s">
@@ -6908,7 +6869,7 @@
       <c r="B213" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C213" s="4">
+      <c r="C213" s="5">
         <v>46220</v>
       </c>
       <c r="D213" s="1" t="s">
@@ -6937,7 +6898,7 @@
       <c r="B214" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C214" s="4">
+      <c r="C214" s="5">
         <v>46220</v>
       </c>
       <c r="D214" s="1" t="s">
@@ -6966,7 +6927,7 @@
       <c r="B215" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C215" s="4">
+      <c r="C215" s="5">
         <v>46223</v>
       </c>
       <c r="D215" s="1" t="s">
@@ -6995,7 +6956,7 @@
       <c r="B216" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C216" s="4">
+      <c r="C216" s="5">
         <v>46226</v>
       </c>
       <c r="D216" s="1" t="s">
@@ -7024,7 +6985,7 @@
       <c r="B217" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C217" s="4">
+      <c r="C217" s="5">
         <v>46223</v>
       </c>
       <c r="D217" s="1" t="s">
@@ -7053,7 +7014,7 @@
       <c r="B218" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C218" s="4">
+      <c r="C218" s="5">
         <v>46225</v>
       </c>
       <c r="D218" s="1" t="s">
@@ -7082,7 +7043,7 @@
       <c r="B219" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C219" s="4">
+      <c r="C219" s="5">
         <v>46225</v>
       </c>
       <c r="D219" s="1" t="s">
@@ -7111,7 +7072,7 @@
       <c r="B220" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C220" s="4">
+      <c r="C220" s="5">
         <v>46225</v>
       </c>
       <c r="D220" s="1" t="s">
@@ -7140,7 +7101,7 @@
       <c r="B221" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C221" s="4">
+      <c r="C221" s="5">
         <v>46224</v>
       </c>
       <c r="D221" s="1" t="s">
@@ -7169,7 +7130,7 @@
       <c r="B222" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C222" s="4">
+      <c r="C222" s="5">
         <v>46225</v>
       </c>
       <c r="D222" s="1" t="s">
@@ -7198,7 +7159,7 @@
       <c r="B223" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C223" s="4">
+      <c r="C223" s="5">
         <v>46227</v>
       </c>
       <c r="D223" s="1" t="s">
@@ -7227,7 +7188,7 @@
       <c r="B224" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C224" s="4">
+      <c r="C224" s="5">
         <v>46227</v>
       </c>
       <c r="D224" s="1" t="s">
@@ -7256,7 +7217,7 @@
       <c r="B225" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C225" s="4">
+      <c r="C225" s="5">
         <v>46227</v>
       </c>
       <c r="D225" s="1" t="s">
@@ -7285,7 +7246,7 @@
       <c r="B226" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C226" s="4">
+      <c r="C226" s="5">
         <v>46218</v>
       </c>
       <c r="D226" s="1" t="s">
@@ -7314,7 +7275,7 @@
       <c r="B227" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C227" s="4">
+      <c r="C227" s="5">
         <v>46224</v>
       </c>
       <c r="D227" s="1" t="s">
@@ -7343,7 +7304,7 @@
       <c r="B228" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C228" s="4">
+      <c r="C228" s="5">
         <v>46212</v>
       </c>
       <c r="D228" s="1" t="s">
@@ -7372,7 +7333,7 @@
       <c r="B229" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C229" s="4">
+      <c r="C229" s="5">
         <v>46216</v>
       </c>
       <c r="D229" s="1" t="s">
@@ -7401,7 +7362,7 @@
       <c r="B230" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C230" s="4">
+      <c r="C230" s="5">
         <v>46225</v>
       </c>
       <c r="D230" s="1" t="s">
@@ -7430,7 +7391,7 @@
       <c r="B231" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C231" s="4">
+      <c r="C231" s="5">
         <v>46224</v>
       </c>
       <c r="D231" s="1" t="s">
@@ -7459,7 +7420,7 @@
       <c r="B232" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C232" s="4">
+      <c r="C232" s="5">
         <v>46225</v>
       </c>
       <c r="D232" s="1" t="s">
@@ -7488,7 +7449,7 @@
       <c r="B233" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C233" s="4">
+      <c r="C233" s="5">
         <v>46226</v>
       </c>
       <c r="D233" s="1" t="s">
@@ -7517,7 +7478,7 @@
       <c r="B234" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C234" s="4">
+      <c r="C234" s="5">
         <v>46225</v>
       </c>
       <c r="D234" s="1" t="s">
@@ -7546,7 +7507,7 @@
       <c r="B235" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C235" s="4">
+      <c r="C235" s="5">
         <v>46230</v>
       </c>
       <c r="D235" s="1" t="s">
@@ -7575,7 +7536,7 @@
       <c r="B236" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C236" s="4">
+      <c r="C236" s="5">
         <v>46224</v>
       </c>
       <c r="D236" s="1" t="s">
@@ -7604,7 +7565,7 @@
       <c r="B237" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C237" s="4">
+      <c r="C237" s="5">
         <v>46217</v>
       </c>
       <c r="D237" s="1" t="s">
@@ -7633,7 +7594,7 @@
       <c r="B238" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C238" s="4">
+      <c r="C238" s="5">
         <v>46226</v>
       </c>
       <c r="D238" s="1" t="s">
@@ -7662,7 +7623,7 @@
       <c r="B239" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C239" s="4">
+      <c r="C239" s="5">
         <v>46231</v>
       </c>
       <c r="D239" s="1" t="s">
@@ -7691,7 +7652,7 @@
       <c r="B240" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C240" s="4">
+      <c r="C240" s="5">
         <v>46226</v>
       </c>
       <c r="D240" s="1" t="s">
@@ -7720,7 +7681,7 @@
       <c r="B241" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C241" s="4">
+      <c r="C241" s="5">
         <v>46225</v>
       </c>
       <c r="D241" s="1" t="s">
@@ -7749,7 +7710,7 @@
       <c r="B242" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C242" s="4">
+      <c r="C242" s="5">
         <v>46216</v>
       </c>
       <c r="D242" s="1" t="s">
@@ -7778,7 +7739,7 @@
       <c r="B243" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C243" s="4">
+      <c r="C243" s="5">
         <v>46223</v>
       </c>
       <c r="D243" s="1" t="s">
@@ -7807,7 +7768,7 @@
       <c r="B244" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C244" s="4">
+      <c r="C244" s="5">
         <v>46230</v>
       </c>
       <c r="D244" s="1" t="s">
@@ -7836,7 +7797,7 @@
       <c r="B245" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C245" s="4">
+      <c r="C245" s="5">
         <v>46234</v>
       </c>
       <c r="D245" s="1" t="s">
@@ -7865,7 +7826,7 @@
       <c r="B246" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C246" s="4">
+      <c r="C246" s="5">
         <v>46233</v>
       </c>
       <c r="D246" s="1" t="s">
@@ -7894,7 +7855,7 @@
       <c r="B247" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C247" s="4">
+      <c r="C247" s="5">
         <v>46233</v>
       </c>
       <c r="D247" s="1" t="s">
@@ -7923,7 +7884,7 @@
       <c r="B248" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C248" s="4">
+      <c r="C248" s="5">
         <v>46234</v>
       </c>
       <c r="D248" s="1" t="s">
@@ -7952,7 +7913,7 @@
       <c r="B249" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C249" s="4">
+      <c r="C249" s="5">
         <v>46233</v>
       </c>
       <c r="D249" s="1" t="s">
@@ -7981,7 +7942,7 @@
       <c r="B250" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C250" s="4">
+      <c r="C250" s="5">
         <v>46234</v>
       </c>
       <c r="D250" s="1" t="s">
@@ -8010,7 +7971,7 @@
       <c r="B251" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C251" s="4">
+      <c r="C251" s="5">
         <v>46233</v>
       </c>
       <c r="D251" s="1" t="s">
@@ -8039,7 +8000,7 @@
       <c r="B252" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C252" s="4">
+      <c r="C252" s="5">
         <v>46240</v>
       </c>
       <c r="D252" s="1" t="s">
@@ -8068,7 +8029,7 @@
       <c r="B253" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C253" s="4">
+      <c r="C253" s="5">
         <v>46240</v>
       </c>
       <c r="D253" s="1" t="s">
@@ -8097,7 +8058,7 @@
       <c r="B254" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C254" s="4">
+      <c r="C254" s="5">
         <v>46240</v>
       </c>
       <c r="D254" s="1" t="s">
@@ -8126,7 +8087,7 @@
       <c r="B255" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C255" s="4">
+      <c r="C255" s="5">
         <v>46239</v>
       </c>
       <c r="D255" s="1" t="s">
@@ -8155,7 +8116,7 @@
       <c r="B256" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C256" s="4">
+      <c r="C256" s="5">
         <v>46240</v>
       </c>
       <c r="D256" s="1" t="s">
@@ -8184,7 +8145,7 @@
       <c r="B257" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C257" s="4">
+      <c r="C257" s="5">
         <v>46239</v>
       </c>
       <c r="D257" s="1" t="s">
@@ -8213,7 +8174,7 @@
       <c r="B258" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C258" s="4">
+      <c r="C258" s="5">
         <v>46240</v>
       </c>
       <c r="D258" s="1" t="s">
@@ -8242,7 +8203,7 @@
       <c r="B259" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C259" s="4">
+      <c r="C259" s="5">
         <v>46239</v>
       </c>
       <c r="D259" s="1" t="s">
@@ -8271,7 +8232,7 @@
       <c r="B260" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C260" s="4">
+      <c r="C260" s="5">
         <v>46241</v>
       </c>
       <c r="D260" s="1" t="s">
@@ -8300,7 +8261,7 @@
       <c r="B261" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C261" s="4">
+      <c r="C261" s="5">
         <v>46240</v>
       </c>
       <c r="D261" s="1" t="s">
@@ -8329,7 +8290,7 @@
       <c r="B262" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C262" s="4">
+      <c r="C262" s="5">
         <v>46238</v>
       </c>
       <c r="D262" s="1" t="s">
@@ -8358,7 +8319,7 @@
       <c r="B263" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C263" s="4">
+      <c r="C263" s="5">
         <v>46238</v>
       </c>
       <c r="D263" s="1" t="s">
@@ -8387,7 +8348,7 @@
       <c r="B264" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C264" s="4">
+      <c r="C264" s="5">
         <v>46216</v>
       </c>
       <c r="D264" s="1" t="s">
@@ -8416,7 +8377,7 @@
       <c r="B265" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C265" s="4">
+      <c r="C265" s="5">
         <v>46225</v>
       </c>
       <c r="D265" s="1" t="s">
@@ -8445,7 +8406,7 @@
       <c r="B266" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C266" s="4">
+      <c r="C266" s="5">
         <v>46230</v>
       </c>
       <c r="D266" s="1" t="s">
@@ -8474,7 +8435,7 @@
       <c r="B267" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C267" s="4">
+      <c r="C267" s="5">
         <v>46217</v>
       </c>
       <c r="D267" s="1" t="s">
@@ -8503,7 +8464,7 @@
       <c r="B268" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C268" s="4">
+      <c r="C268" s="5">
         <v>46219</v>
       </c>
       <c r="D268" s="1" t="s">
@@ -8532,7 +8493,7 @@
       <c r="B269" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C269" s="4">
+      <c r="C269" s="5">
         <v>46227</v>
       </c>
       <c r="D269" s="1" t="s">
@@ -8561,7 +8522,7 @@
       <c r="B270" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C270" s="4">
+      <c r="C270" s="5">
         <v>46244</v>
       </c>
       <c r="D270" s="1" t="s">
@@ -8590,7 +8551,7 @@
       <c r="B271" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C271" s="4">
+      <c r="C271" s="5">
         <v>46246</v>
       </c>
       <c r="D271" s="1" t="s">
@@ -8619,7 +8580,7 @@
       <c r="B272" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C272" s="4">
+      <c r="C272" s="5">
         <v>46244</v>
       </c>
       <c r="D272" s="1" t="s">
@@ -8648,7 +8609,7 @@
       <c r="B273" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C273" s="4">
+      <c r="C273" s="5">
         <v>46246</v>
       </c>
       <c r="D273" s="1" t="s">
@@ -8677,7 +8638,7 @@
       <c r="B274" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C274" s="4">
+      <c r="C274" s="5">
         <v>46244</v>
       </c>
       <c r="D274" s="1" t="s">
@@ -8706,7 +8667,7 @@
       <c r="B275" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C275" s="4">
+      <c r="C275" s="5">
         <v>46247</v>
       </c>
       <c r="D275" s="1" t="s">
@@ -8735,7 +8696,7 @@
       <c r="B276" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C276" s="4">
+      <c r="C276" s="5">
         <v>46244</v>
       </c>
       <c r="D276" s="1" t="s">
@@ -8764,7 +8725,7 @@
       <c r="B277" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C277" s="4">
+      <c r="C277" s="5">
         <v>46246</v>
       </c>
       <c r="D277" s="1" t="s">
@@ -8793,7 +8754,7 @@
       <c r="B278" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C278" s="4">
+      <c r="C278" s="5">
         <v>46244</v>
       </c>
       <c r="D278" s="1" t="s">
@@ -8822,7 +8783,7 @@
       <c r="B279" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C279" s="4">
+      <c r="C279" s="5">
         <v>46246</v>
       </c>
       <c r="D279" s="1" t="s">
@@ -8851,7 +8812,7 @@
       <c r="B280" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C280" s="4">
+      <c r="C280" s="5">
         <v>46244</v>
       </c>
       <c r="D280" s="1" t="s">
@@ -8880,7 +8841,7 @@
       <c r="B281" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C281" s="4">
+      <c r="C281" s="5">
         <v>46246</v>
       </c>
       <c r="D281" s="1" t="s">
@@ -8909,7 +8870,7 @@
       <c r="B282" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C282" s="4">
+      <c r="C282" s="5">
         <v>46247</v>
       </c>
       <c r="D282" s="1" t="s">
@@ -8938,7 +8899,7 @@
       <c r="B283" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C283" s="4">
+      <c r="C283" s="5">
         <v>46245</v>
       </c>
       <c r="D283" s="1" t="s">
@@ -8967,7 +8928,7 @@
       <c r="B284" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C284" s="4">
+      <c r="C284" s="5">
         <v>46245</v>
       </c>
       <c r="D284" s="1" t="s">
@@ -8996,7 +8957,7 @@
       <c r="B285" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C285" s="4">
+      <c r="C285" s="5">
         <v>46246</v>
       </c>
       <c r="D285" s="1" t="s">
@@ -9025,7 +8986,7 @@
       <c r="B286" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C286" s="4">
+      <c r="C286" s="5">
         <v>46245</v>
       </c>
       <c r="D286" s="1" t="s">
@@ -9054,7 +9015,7 @@
       <c r="B287" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C287" s="4">
+      <c r="C287" s="5">
         <v>46245</v>
       </c>
       <c r="D287" s="1" t="s">
@@ -9083,7 +9044,7 @@
       <c r="B288" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C288" s="4">
+      <c r="C288" s="5">
         <v>46245</v>
       </c>
       <c r="D288" s="1" t="s">
@@ -9112,7 +9073,7 @@
       <c r="B289" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C289" s="4">
+      <c r="C289" s="5">
         <v>46245</v>
       </c>
       <c r="D289" s="1" t="s">
@@ -9141,7 +9102,7 @@
       <c r="B290" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C290" s="4">
+      <c r="C290" s="5">
         <v>46245</v>
       </c>
       <c r="D290" s="1" t="s">
@@ -9170,7 +9131,7 @@
       <c r="B291" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C291" s="4">
+      <c r="C291" s="5">
         <v>46244</v>
       </c>
       <c r="D291" s="1" t="s">
@@ -9199,7 +9160,7 @@
       <c r="B292" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C292" s="4">
+      <c r="C292" s="5">
         <v>46248</v>
       </c>
       <c r="D292" s="1" t="s">
@@ -9228,7 +9189,7 @@
       <c r="B293" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C293" s="4">
+      <c r="C293" s="5">
         <v>46247</v>
       </c>
       <c r="D293" s="1" t="s">
@@ -9257,7 +9218,7 @@
       <c r="B294" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C294" s="4">
+      <c r="C294" s="5">
         <v>46251</v>
       </c>
       <c r="D294" s="1" t="s">
@@ -9286,7 +9247,7 @@
       <c r="B295" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C295" s="4">
+      <c r="C295" s="5">
         <v>46252</v>
       </c>
       <c r="D295" s="1" t="s">
@@ -9315,7 +9276,7 @@
       <c r="B296" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C296" s="4">
+      <c r="C296" s="5">
         <v>46252</v>
       </c>
       <c r="D296" s="1" t="s">
@@ -9344,7 +9305,7 @@
       <c r="B297" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C297" s="4">
+      <c r="C297" s="5">
         <v>46252</v>
       </c>
       <c r="D297" s="1" t="s">
@@ -9373,7 +9334,7 @@
       <c r="B298" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C298" s="4">
+      <c r="C298" s="5">
         <v>46251</v>
       </c>
       <c r="D298" s="1" t="s">
@@ -9402,7 +9363,7 @@
       <c r="B299" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C299" s="4">
+      <c r="C299" s="5">
         <v>46251</v>
       </c>
       <c r="D299" s="1" t="s">
@@ -9431,7 +9392,7 @@
       <c r="B300" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C300" s="4">
+      <c r="C300" s="5">
         <v>46252</v>
       </c>
       <c r="D300" s="1" t="s">
@@ -9460,7 +9421,7 @@
       <c r="B301" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C301" s="4">
+      <c r="C301" s="5">
         <v>46254</v>
       </c>
       <c r="D301" s="1" t="s">
@@ -9489,7 +9450,7 @@
       <c r="B302" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C302" s="4">
+      <c r="C302" s="5">
         <v>46251</v>
       </c>
       <c r="D302" s="1" t="s">
@@ -9518,7 +9479,7 @@
       <c r="B303" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C303" s="4">
+      <c r="C303" s="5">
         <v>46253</v>
       </c>
       <c r="D303" s="1" t="s">
@@ -9547,7 +9508,7 @@
       <c r="B304" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C304" s="4">
+      <c r="C304" s="5">
         <v>46253</v>
       </c>
       <c r="D304" s="1" t="s">
@@ -9576,7 +9537,7 @@
       <c r="B305" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C305" s="4">
+      <c r="C305" s="5">
         <v>46252</v>
       </c>
       <c r="D305" s="1" t="s">
@@ -9605,7 +9566,7 @@
       <c r="B306" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C306" s="4">
+      <c r="C306" s="5">
         <v>46251</v>
       </c>
       <c r="D306" s="1" t="s">
@@ -9634,7 +9595,7 @@
       <c r="B307" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C307" s="4">
+      <c r="C307" s="5">
         <v>46251</v>
       </c>
       <c r="D307" s="1" t="s">
@@ -9663,7 +9624,7 @@
       <c r="B308" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C308" s="4">
+      <c r="C308" s="5">
         <v>46251</v>
       </c>
       <c r="D308" s="1" t="s">
@@ -9692,7 +9653,7 @@
       <c r="B309" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C309" s="4">
+      <c r="C309" s="5">
         <v>46253</v>
       </c>
       <c r="D309" s="1" t="s">
@@ -9721,7 +9682,7 @@
       <c r="B310" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C310" s="4">
+      <c r="C310" s="5">
         <v>46251</v>
       </c>
       <c r="D310" s="1" t="s">
@@ -9750,7 +9711,7 @@
       <c r="B311" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C311" s="4">
+      <c r="C311" s="5">
         <v>46252</v>
       </c>
       <c r="D311" s="1" t="s">
@@ -9779,7 +9740,7 @@
       <c r="B312" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C312" s="4">
+      <c r="C312" s="5">
         <v>46254</v>
       </c>
       <c r="D312" s="1" t="s">
@@ -9808,7 +9769,7 @@
       <c r="B313" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C313" s="4">
+      <c r="C313" s="5">
         <v>46255</v>
       </c>
       <c r="D313" s="1" t="s">
@@ -9837,7 +9798,7 @@
       <c r="B314" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C314" s="4">
+      <c r="C314" s="5">
         <v>46255</v>
       </c>
       <c r="D314" s="1" t="s">
@@ -9866,7 +9827,7 @@
       <c r="B315" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C315" s="4">
+      <c r="C315" s="5">
         <v>46255</v>
       </c>
       <c r="D315" s="1" t="s">
@@ -9895,7 +9856,7 @@
       <c r="B316" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C316" s="4">
+      <c r="C316" s="5">
         <v>46255</v>
       </c>
       <c r="D316" s="1" t="s">
@@ -9924,7 +9885,7 @@
       <c r="B317" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C317" s="4">
+      <c r="C317" s="5">
         <v>46258</v>
       </c>
       <c r="D317" s="1" t="s">
@@ -9953,7 +9914,7 @@
       <c r="B318" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C318" s="4">
+      <c r="C318" s="5">
         <v>46258</v>
       </c>
       <c r="D318" s="1" t="s">
@@ -9982,7 +9943,7 @@
       <c r="B319" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C319" s="4">
+      <c r="C319" s="5">
         <v>46261</v>
       </c>
       <c r="D319" s="1" t="s">
@@ -10011,7 +9972,7 @@
       <c r="B320" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C320" s="4">
+      <c r="C320" s="5">
         <v>46258</v>
       </c>
       <c r="D320" s="1" t="s">
@@ -10040,7 +10001,7 @@
       <c r="B321" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C321" s="4">
+      <c r="C321" s="5">
         <v>46260</v>
       </c>
       <c r="D321" s="1" t="s">
@@ -10069,7 +10030,7 @@
       <c r="B322" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C322" s="4">
+      <c r="C322" s="5">
         <v>46262</v>
       </c>
       <c r="D322" s="1" t="s">
@@ -10098,7 +10059,7 @@
       <c r="B323" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C323" s="4">
+      <c r="C323" s="5">
         <v>46262</v>
       </c>
       <c r="D323" s="1" t="s">
@@ -10127,7 +10088,7 @@
       <c r="B324" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C324" s="4">
+      <c r="C324" s="5">
         <v>46262</v>
       </c>
       <c r="D324" s="1" t="s">
@@ -10156,7 +10117,7 @@
       <c r="B325" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C325" s="4">
+      <c r="C325" s="5">
         <v>46262</v>
       </c>
       <c r="D325" s="1" t="s">
@@ -10185,7 +10146,7 @@
       <c r="B326" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C326" s="4">
+      <c r="C326" s="5">
         <v>46261</v>
       </c>
       <c r="D326" s="1" t="s">
@@ -10209,13 +10170,13 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C327" s="4">
-        <v>46268</v>
+        <v>10</v>
+      </c>
+      <c r="C327" s="5">
+        <v>46262</v>
       </c>
       <c r="D327" s="1" t="s">
         <v>11</v>
@@ -10224,13 +10185,13 @@
         <v>12</v>
       </c>
       <c r="F327" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G327" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H327" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I327" s="1">
         <v>2026</v>
@@ -10238,28 +10199,28 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C328" s="4">
-        <v>46268</v>
+        <v>10</v>
+      </c>
+      <c r="C328" s="5">
+        <v>46262</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F328" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G328" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="I328" s="1">
         <v>2026</v>
@@ -10267,13 +10228,13 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C329" s="4">
-        <v>46267</v>
+      <c r="C329" s="5">
+        <v>46268</v>
       </c>
       <c r="D329" s="1" t="s">
         <v>11</v>
@@ -10282,10 +10243,10 @@
         <v>12</v>
       </c>
       <c r="F329" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G329" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H329" s="1" t="s">
         <v>37</v>
@@ -10296,16 +10257,16 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C330" s="4">
-        <v>46267</v>
+      <c r="C330" s="5">
+        <v>46268</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E330" s="1" t="s">
         <v>12</v>
@@ -10325,13 +10286,13 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C331" s="4">
-        <v>46268</v>
+      <c r="C331" s="5">
+        <v>46267</v>
       </c>
       <c r="D331" s="1" t="s">
         <v>11</v>
@@ -10340,10 +10301,10 @@
         <v>12</v>
       </c>
       <c r="F331" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G331" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H331" s="1" t="s">
         <v>37</v>
@@ -10354,25 +10315,25 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C332" s="4">
-        <v>46268</v>
+        <v>19</v>
+      </c>
+      <c r="C332" s="5">
+        <v>46267</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F332" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G332" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H332" s="1" t="s">
         <v>37</v>
@@ -10383,13 +10344,13 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C333" s="4">
-        <v>46267</v>
+        <v>19</v>
+      </c>
+      <c r="C333" s="5">
+        <v>46268</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>11</v>
@@ -10412,12 +10373,12 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C334" s="4">
+      <c r="C334" s="5">
         <v>46266</v>
       </c>
       <c r="D334" s="1" t="s">
@@ -10441,13 +10402,13 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C335" s="4">
-        <v>46274</v>
+      <c r="C335" s="5">
+        <v>46273</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>11</v>
@@ -10470,13 +10431,13 @@
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B336" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C336" s="4">
-        <v>46266</v>
+      <c r="C336" s="5">
+        <v>46274</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>11</v>
@@ -10499,25 +10460,25 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B337" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C337" s="4">
-        <v>46275</v>
+        <v>10</v>
+      </c>
+      <c r="C337" s="5">
+        <v>46276</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F337" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G337" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H337" s="1" t="s">
         <v>37</v>
@@ -10528,13 +10489,13 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C338" s="4">
-        <v>46274</v>
+        <v>10</v>
+      </c>
+      <c r="C338" s="5">
+        <v>46276</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>11</v>
@@ -10543,10 +10504,10 @@
         <v>12</v>
       </c>
       <c r="F338" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G338" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H338" s="1" t="s">
         <v>37</v>
@@ -10557,13 +10518,13 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C339" s="4">
-        <v>46275</v>
+        <v>10</v>
+      </c>
+      <c r="C339" s="5">
+        <v>46280</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>11</v>
@@ -10572,10 +10533,10 @@
         <v>12</v>
       </c>
       <c r="F339" s="1">
-        <v>100</v>
-      </c>
-      <c r="G339" s="2">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="G339" s="6">
+        <v>0.95</v>
       </c>
       <c r="H339" s="1" t="s">
         <v>37</v>
@@ -10586,13 +10547,13 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C340" s="4">
-        <v>46273</v>
+        <v>10</v>
+      </c>
+      <c r="C340" s="5">
+        <v>46266</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>11</v>
@@ -10601,10 +10562,10 @@
         <v>12</v>
       </c>
       <c r="F340" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G340" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H340" s="1" t="s">
         <v>37</v>
@@ -10615,16 +10576,16 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C341" s="4">
-        <v>46273</v>
+        <v>10</v>
+      </c>
+      <c r="C341" s="5">
+        <v>46276</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>12</v>
@@ -10644,13 +10605,13 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C342" s="4">
-        <v>46274</v>
+      <c r="C342" s="5">
+        <v>46275</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>11</v>
@@ -10659,10 +10620,10 @@
         <v>12</v>
       </c>
       <c r="F342" s="1">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="G342" s="2">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>37</v>
@@ -10673,13 +10634,13 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C343" s="4">
-        <v>46273</v>
+      <c r="C343" s="5">
+        <v>46274</v>
       </c>
       <c r="D343" s="1" t="s">
         <v>11</v>
@@ -10688,10 +10649,10 @@
         <v>12</v>
       </c>
       <c r="F343" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G343" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H343" s="1" t="s">
         <v>37</v>
@@ -10702,13 +10663,13 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C344" s="4">
-        <v>46273</v>
+      <c r="C344" s="5">
+        <v>46275</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>11</v>
@@ -10717,10 +10678,10 @@
         <v>12</v>
       </c>
       <c r="F344" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G344" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H344" s="1" t="s">
         <v>37</v>
@@ -10731,13 +10692,13 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C345" s="4">
-        <v>46275</v>
+      <c r="C345" s="5">
+        <v>46273</v>
       </c>
       <c r="D345" s="1" t="s">
         <v>11</v>
@@ -10746,10 +10707,10 @@
         <v>12</v>
       </c>
       <c r="F345" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G345" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H345" s="1" t="s">
         <v>37</v>
@@ -10760,13 +10721,13 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C346" s="4">
-        <v>46275</v>
+      <c r="C346" s="5">
+        <v>46273</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>11</v>
@@ -10789,13 +10750,13 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B347" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C347" s="4">
-        <v>46273</v>
+        <v>19</v>
+      </c>
+      <c r="C347" s="5">
+        <v>46274</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>11</v>
@@ -10804,10 +10765,10 @@
         <v>12</v>
       </c>
       <c r="F347" s="1">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G347" s="2">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="H347" s="1" t="s">
         <v>37</v>
@@ -10818,13 +10779,13 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C348" s="4">
-        <v>46276</v>
+        <v>19</v>
+      </c>
+      <c r="C348" s="5">
+        <v>46273</v>
       </c>
       <c r="D348" s="1" t="s">
         <v>11</v>
@@ -10847,13 +10808,13 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C349" s="4">
-        <v>46275</v>
+        <v>19</v>
+      </c>
+      <c r="C349" s="5">
+        <v>46273</v>
       </c>
       <c r="D349" s="1" t="s">
         <v>11</v>
@@ -10876,13 +10837,13 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C350" s="4">
-        <v>46274</v>
+        <v>19</v>
+      </c>
+      <c r="C350" s="5">
+        <v>46275</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>11</v>
@@ -10904,205 +10865,756 @@
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A351" s="5" t="s">
+      <c r="A351" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B351" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C351" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D351" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E351" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F351" s="1">
+        <v>100</v>
+      </c>
+      <c r="G351" s="2">
+        <v>1</v>
+      </c>
+      <c r="H351" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I351" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B352" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C352" s="5">
+        <v>46276</v>
+      </c>
+      <c r="D352" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E352" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="1">
+        <v>100</v>
+      </c>
+      <c r="G352" s="2">
+        <v>1</v>
+      </c>
+      <c r="H352" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I352" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B351" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C351" s="6">
+      <c r="B353" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C353" s="5">
+        <v>46268</v>
+      </c>
+      <c r="D353" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E353" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F353" s="1">
+        <v>90</v>
+      </c>
+      <c r="G353" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H353" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I353" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B354" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="5">
         <v>46275</v>
       </c>
-      <c r="D351" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E351" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F351" s="5">
-        <v>100</v>
-      </c>
-      <c r="G351" s="7">
-        <v>1</v>
-      </c>
-      <c r="H351" s="5" t="s">
+      <c r="D354" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="1">
+        <v>100</v>
+      </c>
+      <c r="G354" s="2">
+        <v>1</v>
+      </c>
+      <c r="H354" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I351" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A352" s="5" t="s">
+      <c r="I354" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B352" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C352" s="6">
+      <c r="B355" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="5">
         <v>46267</v>
       </c>
-      <c r="D352" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E352" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F352" s="5">
-        <v>100</v>
-      </c>
-      <c r="G352" s="7">
-        <v>1</v>
-      </c>
-      <c r="H352" s="5" t="s">
+      <c r="D355" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E355" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F355" s="1">
+        <v>100</v>
+      </c>
+      <c r="G355" s="2">
+        <v>1</v>
+      </c>
+      <c r="H355" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I352" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A353" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B353" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C353" s="6">
+      <c r="I355" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B356" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D356" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E356" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F356" s="1">
+        <v>100</v>
+      </c>
+      <c r="G356" s="2">
+        <v>1</v>
+      </c>
+      <c r="H356" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I356" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B357" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D357" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E357" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F357" s="1">
+        <v>95</v>
+      </c>
+      <c r="G357" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="H357" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I357" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B358" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" s="5">
+        <v>46267</v>
+      </c>
+      <c r="D358" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E358" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F358" s="1">
+        <v>100</v>
+      </c>
+      <c r="G358" s="2">
+        <v>1</v>
+      </c>
+      <c r="H358" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I358" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359" s="5">
+        <v>46273</v>
+      </c>
+      <c r="D359" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E359" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F359" s="1">
+        <v>90</v>
+      </c>
+      <c r="G359" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="H359" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I359" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B360" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C360" s="5">
         <v>46276</v>
       </c>
-      <c r="D353" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E353" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F353" s="5">
-        <v>100</v>
-      </c>
-      <c r="G353" s="7">
-        <v>1</v>
-      </c>
-      <c r="H353" s="5" t="s">
+      <c r="D360" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E360" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F360" s="1">
+        <v>100</v>
+      </c>
+      <c r="G360" s="2">
+        <v>1</v>
+      </c>
+      <c r="H360" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I353" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A354" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B354" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C354" s="6">
-        <v>46276</v>
-      </c>
-      <c r="D354" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E354" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F354" s="5">
-        <v>100</v>
-      </c>
-      <c r="G354" s="7">
-        <v>1</v>
-      </c>
-      <c r="H354" s="5" t="s">
+      <c r="I360" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B361" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C361" s="5">
+        <v>46266</v>
+      </c>
+      <c r="D361" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E361" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F361" s="1">
+        <v>95</v>
+      </c>
+      <c r="G361" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H361" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I354" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A355" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B355" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C355" s="6">
-        <v>46276</v>
-      </c>
-      <c r="D355" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E355" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F355" s="5">
-        <v>100</v>
-      </c>
-      <c r="G355" s="7">
-        <v>1</v>
-      </c>
-      <c r="H355" s="5" t="s">
+      <c r="I361" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B362" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C362" s="5">
+        <v>46275</v>
+      </c>
+      <c r="D362" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E362" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F362" s="1">
+        <v>95</v>
+      </c>
+      <c r="G362" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H362" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I355" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A356" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B356" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C356" s="6">
-        <v>46276</v>
-      </c>
-      <c r="D356" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E356" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F356" s="5">
-        <v>100</v>
-      </c>
-      <c r="G356" s="7">
-        <v>1</v>
-      </c>
-      <c r="H356" s="5" t="s">
+      <c r="I362" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B363" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C363" s="5">
+        <v>46274</v>
+      </c>
+      <c r="D363" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E363" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F363" s="1">
+        <v>100</v>
+      </c>
+      <c r="G363" s="2">
+        <v>1</v>
+      </c>
+      <c r="H363" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I356" s="5">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A357" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B357" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C357" s="6">
-        <v>46273</v>
-      </c>
-      <c r="D357" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E357" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F357" s="5">
-        <v>100</v>
-      </c>
-      <c r="G357" s="7">
-        <v>1</v>
-      </c>
-      <c r="H357" s="5" t="s">
+      <c r="I363" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B364" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C364" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D364" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E364" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F364" s="1">
+        <v>100</v>
+      </c>
+      <c r="G364" s="6">
+        <v>1</v>
+      </c>
+      <c r="H364" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="I357" s="5">
+      <c r="I364" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B365" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C365" s="5">
+        <v>46280</v>
+      </c>
+      <c r="D365" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E365" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F365" s="1">
+        <v>100</v>
+      </c>
+      <c r="G365" s="6">
+        <v>1</v>
+      </c>
+      <c r="H365" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I365" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B366" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C366" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D366" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E366" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F366" s="1">
+        <v>100</v>
+      </c>
+      <c r="G366" s="6">
+        <v>1</v>
+      </c>
+      <c r="H366" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I366" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B367" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C367" s="5">
+        <v>46280</v>
+      </c>
+      <c r="D367" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E367" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F367" s="1">
+        <v>100</v>
+      </c>
+      <c r="G367" s="6">
+        <v>1</v>
+      </c>
+      <c r="H367" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I367" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B368" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C368" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D368" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E368" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F368" s="1">
+        <v>100</v>
+      </c>
+      <c r="G368" s="6">
+        <v>1</v>
+      </c>
+      <c r="H368" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I368" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B369" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C369" s="5">
+        <v>46281</v>
+      </c>
+      <c r="D369" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E369" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F369" s="1">
+        <v>100</v>
+      </c>
+      <c r="G369" s="6">
+        <v>1</v>
+      </c>
+      <c r="H369" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I369" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B370" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C370" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D370" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E370" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F370" s="1">
+        <v>100</v>
+      </c>
+      <c r="G370" s="6">
+        <v>1</v>
+      </c>
+      <c r="H370" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I370" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B371" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C371" s="5">
+        <v>46282</v>
+      </c>
+      <c r="D371" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E371" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F371" s="1">
+        <v>100</v>
+      </c>
+      <c r="G371" s="6">
+        <v>1</v>
+      </c>
+      <c r="H371" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I371" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B372" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C372" s="5">
+        <v>46280</v>
+      </c>
+      <c r="D372" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E372" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F372" s="1">
+        <v>100</v>
+      </c>
+      <c r="G372" s="6">
+        <v>1</v>
+      </c>
+      <c r="H372" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I372" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B373" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C373" s="5">
+        <v>46281</v>
+      </c>
+      <c r="D373" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E373" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F373" s="1">
+        <v>100</v>
+      </c>
+      <c r="G373" s="6">
+        <v>1</v>
+      </c>
+      <c r="H373" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I373" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C374" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D374" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E374" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F374" s="1">
+        <v>100</v>
+      </c>
+      <c r="G374" s="6">
+        <v>1</v>
+      </c>
+      <c r="H374" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I374" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B375" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C375" s="5">
+        <v>46281</v>
+      </c>
+      <c r="D375" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E375" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F375" s="1">
+        <v>100</v>
+      </c>
+      <c r="G375" s="6">
+        <v>1</v>
+      </c>
+      <c r="H375" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I375" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B376" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C376" s="5">
+        <v>46279</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E376" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F376" s="1">
+        <v>100</v>
+      </c>
+      <c r="G376" s="6">
+        <v>1</v>
+      </c>
+      <c r="H376" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I376" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -11127,19 +11639,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11493,6 +12005,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bbf009f58139d30e700e9d9dd8708ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bbfb5a56ff61f0f4bba1626b54b38306" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -11749,15 +12270,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11773,6 +12285,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B400D-C15B-4808-975D-D6FB017A04F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11791,27 +12311,19 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
     <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC2FBD7-0487-49CA-8C3C-920C17CA81EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6888D363-961D-423C-88B7-5F782EAB4A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="15" windowWidth="21525" windowHeight="20880" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="18405" yWindow="270" windowWidth="20745" windowHeight="20880" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -286,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -299,9 +299,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -349,10 +346,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I376" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I376" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I373">
-    <sortCondition ref="A1:A373"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I383" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I383" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I374">
+    <sortCondition ref="A1:A374"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{F3FB1979-6840-4EDA-8F75-C44587A3E01A}" name="AssociateName"/>
@@ -700,18 +697,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I376"/>
+  <dimension ref="A1:I383"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.140625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="37.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6052,25 +6049,25 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C185" s="5">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F185" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G185" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H185" s="1" t="s">
         <v>32</v>
@@ -6081,13 +6078,13 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C186" s="5">
-        <v>46209</v>
+        <v>46219</v>
       </c>
       <c r="D186" s="1" t="s">
         <v>11</v>
@@ -6116,7 +6113,7 @@
         <v>19</v>
       </c>
       <c r="C187" s="5">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="D187" s="1" t="s">
         <v>11</v>
@@ -6139,13 +6136,13 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C188" s="5">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>11</v>
@@ -6168,16 +6165,16 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C189" s="5">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
@@ -6197,13 +6194,13 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C190" s="5">
-        <v>46210</v>
+        <v>46230</v>
       </c>
       <c r="D190" s="1" t="s">
         <v>11</v>
@@ -6226,13 +6223,13 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C191" s="5">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>11</v>
@@ -6255,13 +6252,13 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C192" s="5">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>11</v>
@@ -6270,10 +6267,10 @@
         <v>12</v>
       </c>
       <c r="F192" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G192" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H192" s="1" t="s">
         <v>32</v>
@@ -6284,13 +6281,13 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C193" s="5">
-        <v>46212</v>
+        <v>46220</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>11</v>
@@ -6299,10 +6296,10 @@
         <v>12</v>
       </c>
       <c r="F193" s="1">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G193" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>32</v>
@@ -6313,25 +6310,25 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C194" s="5">
-        <v>46212</v>
+        <v>46227</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F194" s="1">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G194" s="2">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="H194" s="1" t="s">
         <v>32</v>
@@ -6342,13 +6339,13 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C195" s="5">
-        <v>46212</v>
+        <v>46224</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>12</v>
@@ -6357,10 +6354,10 @@
         <v>12</v>
       </c>
       <c r="F195" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G195" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>32</v>
@@ -6371,25 +6368,25 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C196" s="5">
-        <v>46213</v>
+        <v>46234</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F196" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G196" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H196" s="1" t="s">
         <v>32</v>
@@ -6400,13 +6397,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C197" s="5">
-        <v>46218</v>
+        <v>46212</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>11</v>
@@ -6429,10 +6426,10 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C198" s="5">
         <v>46216</v>
@@ -6444,10 +6441,10 @@
         <v>12</v>
       </c>
       <c r="F198" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G198" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>32</v>
@@ -6458,13 +6455,13 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C199" s="5">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>11</v>
@@ -6487,13 +6484,13 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C200" s="5">
-        <v>46219</v>
+        <v>46227</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>11</v>
@@ -6522,10 +6519,10 @@
         <v>19</v>
       </c>
       <c r="C201" s="5">
-        <v>46216</v>
+        <v>46227</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>12</v>
@@ -6545,13 +6542,13 @@
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C202" s="5">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>11</v>
@@ -6574,13 +6571,13 @@
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C203" s="5">
-        <v>46219</v>
+        <v>46210</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>11</v>
@@ -6603,7 +6600,7 @@
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>10</v>
@@ -6618,10 +6615,10 @@
         <v>12</v>
       </c>
       <c r="F204" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G204" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H204" s="1" t="s">
         <v>32</v>
@@ -6632,13 +6629,13 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C205" s="5">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>11</v>
@@ -6661,13 +6658,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C206" s="5">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>11</v>
@@ -6690,13 +6687,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C207" s="5">
-        <v>46218</v>
+        <v>46226</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>11</v>
@@ -6719,13 +6716,13 @@
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C208" s="5">
-        <v>46216</v>
+        <v>46234</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>11</v>
@@ -6734,10 +6731,10 @@
         <v>12</v>
       </c>
       <c r="F208" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G208" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H208" s="1" t="s">
         <v>32</v>
@@ -6748,25 +6745,25 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C209" s="5">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F209" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G209" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" s="1" t="s">
         <v>32</v>
@@ -6777,13 +6774,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C210" s="5">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>11</v>
@@ -6792,10 +6789,10 @@
         <v>12</v>
       </c>
       <c r="F210" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G210" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>32</v>
@@ -6806,16 +6803,16 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C211" s="5">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E211" s="1" t="s">
         <v>12</v>
@@ -6835,13 +6832,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C212" s="5">
-        <v>46219</v>
+        <v>46216</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>11</v>
@@ -6864,13 +6861,13 @@
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C213" s="5">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>11</v>
@@ -6893,25 +6890,25 @@
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C214" s="5">
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="D214" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F214" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G214" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H214" s="1" t="s">
         <v>32</v>
@@ -6922,13 +6919,13 @@
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C215" s="5">
-        <v>46223</v>
+        <v>46212</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>11</v>
@@ -6951,13 +6948,13 @@
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C216" s="5">
-        <v>46226</v>
+        <v>46219</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>11</v>
@@ -6980,13 +6977,13 @@
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C217" s="5">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>11</v>
@@ -7009,13 +7006,13 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C218" s="5">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>11</v>
@@ -7024,10 +7021,10 @@
         <v>12</v>
       </c>
       <c r="F218" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G218" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H218" s="1" t="s">
         <v>32</v>
@@ -7044,19 +7041,19 @@
         <v>19</v>
       </c>
       <c r="C219" s="5">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F219" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G219" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H219" s="1" t="s">
         <v>32</v>
@@ -7067,7 +7064,7 @@
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>19</v>
@@ -7076,16 +7073,16 @@
         <v>46225</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F220" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G220" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H220" s="1" t="s">
         <v>32</v>
@@ -7096,25 +7093,25 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C221" s="5">
-        <v>46224</v>
+        <v>46210</v>
       </c>
       <c r="D221" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G221" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" s="1" t="s">
         <v>32</v>
@@ -7125,13 +7122,13 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C222" s="5">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="D222" s="1" t="s">
         <v>11</v>
@@ -7140,10 +7137,10 @@
         <v>12</v>
       </c>
       <c r="F222" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G222" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H222" s="1" t="s">
         <v>32</v>
@@ -7154,13 +7151,13 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C223" s="5">
-        <v>46227</v>
+        <v>46219</v>
       </c>
       <c r="D223" s="1" t="s">
         <v>11</v>
@@ -7169,10 +7166,10 @@
         <v>12</v>
       </c>
       <c r="F223" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G223" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H223" s="1" t="s">
         <v>32</v>
@@ -7183,13 +7180,13 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C224" s="5">
-        <v>46227</v>
+        <v>46226</v>
       </c>
       <c r="D224" s="1" t="s">
         <v>11</v>
@@ -7212,16 +7209,16 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C225" s="5">
-        <v>46227</v>
+        <v>46225</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E225" s="1" t="s">
         <v>12</v>
@@ -7241,13 +7238,13 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C226" s="5">
-        <v>46218</v>
+        <v>46233</v>
       </c>
       <c r="D226" s="1" t="s">
         <v>11</v>
@@ -7270,25 +7267,25 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C227" s="5">
-        <v>46224</v>
+        <v>46233</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F227" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G227" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H227" s="1" t="s">
         <v>32</v>
@@ -7299,13 +7296,13 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C228" s="5">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="D228" s="1" t="s">
         <v>11</v>
@@ -7314,10 +7311,10 @@
         <v>12</v>
       </c>
       <c r="F228" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G228" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H228" s="1" t="s">
         <v>32</v>
@@ -7328,25 +7325,25 @@
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C229" s="5">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E229" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F229" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G229" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H229" s="1" t="s">
         <v>32</v>
@@ -7357,13 +7354,13 @@
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C230" s="5">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="D230" s="1" t="s">
         <v>11</v>
@@ -7372,10 +7369,10 @@
         <v>12</v>
       </c>
       <c r="F230" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G230" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H230" s="1" t="s">
         <v>32</v>
@@ -7444,13 +7441,13 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C233" s="5">
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="D233" s="1" t="s">
         <v>11</v>
@@ -7473,25 +7470,25 @@
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C234" s="5">
-        <v>46225</v>
+        <v>46205</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E234" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F234" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G234" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H234" s="1" t="s">
         <v>32</v>
@@ -7508,7 +7505,7 @@
         <v>19</v>
       </c>
       <c r="C235" s="5">
-        <v>46230</v>
+        <v>46218</v>
       </c>
       <c r="D235" s="1" t="s">
         <v>11</v>
@@ -7540,16 +7537,16 @@
         <v>46224</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F236" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G236" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H236" s="1" t="s">
         <v>32</v>
@@ -7566,7 +7563,7 @@
         <v>19</v>
       </c>
       <c r="C237" s="5">
-        <v>46217</v>
+        <v>46230</v>
       </c>
       <c r="D237" s="1" t="s">
         <v>11</v>
@@ -7589,25 +7586,25 @@
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C238" s="5">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E238" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F238" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G238" s="2">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="H238" s="1" t="s">
         <v>32</v>
@@ -7618,13 +7615,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C239" s="5">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="D239" s="1" t="s">
         <v>11</v>
@@ -7647,13 +7644,13 @@
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C240" s="5">
-        <v>46226</v>
+        <v>46212</v>
       </c>
       <c r="D240" s="1" t="s">
         <v>11</v>
@@ -7676,13 +7673,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C241" s="5">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="D241" s="1" t="s">
         <v>11</v>
@@ -7705,13 +7702,13 @@
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C242" s="5">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="D242" s="1" t="s">
         <v>11</v>
@@ -7734,25 +7731,25 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C243" s="5">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E243" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F243" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G243" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H243" s="1" t="s">
         <v>32</v>
@@ -7763,13 +7760,13 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C244" s="5">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="D244" s="1" t="s">
         <v>11</v>
@@ -7827,10 +7824,10 @@
         <v>10</v>
       </c>
       <c r="C246" s="5">
-        <v>46233</v>
+        <v>46212</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E246" s="1" t="s">
         <v>12</v>
@@ -7850,13 +7847,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C247" s="5">
-        <v>46233</v>
+        <v>46216</v>
       </c>
       <c r="D247" s="1" t="s">
         <v>11</v>
@@ -7865,10 +7862,10 @@
         <v>12</v>
       </c>
       <c r="F247" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G247" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H247" s="1" t="s">
         <v>32</v>
@@ -7879,25 +7876,25 @@
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B248" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C248" s="5">
-        <v>46234</v>
+        <v>46220</v>
       </c>
       <c r="D248" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F248" s="1">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G248" s="2">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="H248" s="1" t="s">
         <v>32</v>
@@ -7908,13 +7905,13 @@
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C249" s="5">
-        <v>46233</v>
+        <v>46226</v>
       </c>
       <c r="D249" s="1" t="s">
         <v>11</v>
@@ -7937,13 +7934,13 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C250" s="5">
-        <v>46234</v>
+        <v>46225</v>
       </c>
       <c r="D250" s="1" t="s">
         <v>11</v>
@@ -7952,10 +7949,10 @@
         <v>12</v>
       </c>
       <c r="F250" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G250" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H250" s="1" t="s">
         <v>32</v>
@@ -7966,7 +7963,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>10</v>
@@ -7978,13 +7975,13 @@
         <v>11</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F251" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G251" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" s="1" t="s">
         <v>32</v>
@@ -8343,25 +8340,25 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C264" s="5">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E264" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F264" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G264" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H264" s="1" t="s">
         <v>32</v>
@@ -8372,13 +8369,13 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C265" s="5">
-        <v>46225</v>
+        <v>46218</v>
       </c>
       <c r="D265" s="1" t="s">
         <v>11</v>
@@ -8401,13 +8398,13 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C266" s="5">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="D266" s="1" t="s">
         <v>11</v>
@@ -9124,7 +9121,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="0.75" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>17</v>
       </c>
@@ -10199,28 +10196,28 @@
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C328" s="5">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="D328" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F328" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G328" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H328" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I328" s="1">
         <v>2026</v>
@@ -10228,7 +10225,7 @@
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B329" s="1" t="s">
         <v>19</v>
@@ -10257,13 +10254,13 @@
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B330" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C330" s="5">
-        <v>46268</v>
+        <v>46267</v>
       </c>
       <c r="D330" s="1" t="s">
         <v>11</v>
@@ -10272,10 +10269,10 @@
         <v>12</v>
       </c>
       <c r="F330" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G330" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H330" s="1" t="s">
         <v>37</v>
@@ -10286,7 +10283,7 @@
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B331" s="1" t="s">
         <v>19</v>
@@ -10295,16 +10292,16 @@
         <v>46267</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E331" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F331" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G331" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H331" s="1" t="s">
         <v>37</v>
@@ -10315,16 +10312,16 @@
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B332" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C332" s="5">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E332" s="1" t="s">
         <v>12</v>
@@ -10344,13 +10341,13 @@
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B333" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C333" s="5">
-        <v>46268</v>
+        <v>46274</v>
       </c>
       <c r="D333" s="1" t="s">
         <v>11</v>
@@ -10373,25 +10370,25 @@
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B334" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C334" s="5">
-        <v>46266</v>
+        <v>46276</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E334" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F334" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G334" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H334" s="1" t="s">
         <v>37</v>
@@ -10402,13 +10399,13 @@
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B335" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C335" s="5">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D335" s="1" t="s">
         <v>11</v>
@@ -10437,7 +10434,7 @@
         <v>10</v>
       </c>
       <c r="C336" s="5">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="D336" s="1" t="s">
         <v>11</v>
@@ -10446,10 +10443,10 @@
         <v>12</v>
       </c>
       <c r="F336" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G336" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H336" s="1" t="s">
         <v>37</v>
@@ -10460,16 +10457,16 @@
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B337" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C337" s="5">
-        <v>46276</v>
+        <v>46266</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E337" s="1" t="s">
         <v>12</v>
@@ -10489,13 +10486,13 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B338" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C338" s="5">
-        <v>46276</v>
+        <v>46275</v>
       </c>
       <c r="D338" s="1" t="s">
         <v>11</v>
@@ -10504,10 +10501,10 @@
         <v>12</v>
       </c>
       <c r="F338" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G338" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H338" s="1" t="s">
         <v>37</v>
@@ -10518,13 +10515,13 @@
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B339" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C339" s="5">
-        <v>46280</v>
+        <v>46274</v>
       </c>
       <c r="D339" s="1" t="s">
         <v>11</v>
@@ -10535,7 +10532,7 @@
       <c r="F339" s="1">
         <v>95</v>
       </c>
-      <c r="G339" s="6">
+      <c r="G339" s="2">
         <v>0.95</v>
       </c>
       <c r="H339" s="1" t="s">
@@ -10547,13 +10544,13 @@
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B340" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C340" s="5">
-        <v>46266</v>
+        <v>46275</v>
       </c>
       <c r="D340" s="1" t="s">
         <v>11</v>
@@ -10576,25 +10573,25 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B341" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C341" s="5">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F341" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G341" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H341" s="1" t="s">
         <v>37</v>
@@ -10605,13 +10602,13 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B342" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C342" s="5">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="D342" s="1" t="s">
         <v>11</v>
@@ -10620,10 +10617,10 @@
         <v>12</v>
       </c>
       <c r="F342" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G342" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>37</v>
@@ -10634,7 +10631,7 @@
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B343" s="1" t="s">
         <v>19</v>
@@ -10649,10 +10646,10 @@
         <v>12</v>
       </c>
       <c r="F343" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G343" s="2">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H343" s="1" t="s">
         <v>37</v>
@@ -10663,13 +10660,13 @@
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B344" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C344" s="5">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="D344" s="1" t="s">
         <v>11</v>
@@ -10692,7 +10689,7 @@
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B345" s="1" t="s">
         <v>19</v>
@@ -10721,13 +10718,13 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B346" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C346" s="5">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="D346" s="1" t="s">
         <v>11</v>
@@ -10750,13 +10747,13 @@
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B347" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C347" s="5">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="D347" s="1" t="s">
         <v>11</v>
@@ -10765,10 +10762,10 @@
         <v>12</v>
       </c>
       <c r="F347" s="1">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G347" s="2">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H347" s="1" t="s">
         <v>37</v>
@@ -10779,16 +10776,16 @@
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C348" s="5">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>12</v>
@@ -10808,25 +10805,25 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B349" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C349" s="5">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F349" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G349" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H349" s="1" t="s">
         <v>37</v>
@@ -10837,13 +10834,13 @@
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B350" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C350" s="5">
-        <v>46275</v>
+        <v>46268</v>
       </c>
       <c r="D350" s="1" t="s">
         <v>11</v>
@@ -10852,10 +10849,10 @@
         <v>12</v>
       </c>
       <c r="F350" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G350" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H350" s="1" t="s">
         <v>37</v>
@@ -10866,10 +10863,10 @@
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B351" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C351" s="5">
         <v>46275</v>
@@ -10895,13 +10892,13 @@
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B352" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C352" s="5">
-        <v>46276</v>
+        <v>46267</v>
       </c>
       <c r="D352" s="1" t="s">
         <v>12</v>
@@ -10930,7 +10927,7 @@
         <v>10</v>
       </c>
       <c r="C353" s="5">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="D353" s="1" t="s">
         <v>11</v>
@@ -10939,10 +10936,10 @@
         <v>12</v>
       </c>
       <c r="F353" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G353" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H353" s="1" t="s">
         <v>37</v>
@@ -10959,7 +10956,7 @@
         <v>10</v>
       </c>
       <c r="C354" s="5">
-        <v>46275</v>
+        <v>46281</v>
       </c>
       <c r="D354" s="1" t="s">
         <v>11</v>
@@ -10982,16 +10979,16 @@
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B355" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C355" s="5">
-        <v>46267</v>
+        <v>46266</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>12</v>
@@ -11017,7 +11014,7 @@
         <v>10</v>
       </c>
       <c r="C356" s="5">
-        <v>46266</v>
+        <v>46279</v>
       </c>
       <c r="D356" s="1" t="s">
         <v>11</v>
@@ -11026,10 +11023,10 @@
         <v>12</v>
       </c>
       <c r="F356" s="1">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="G356" s="2">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="H356" s="1" t="s">
         <v>37</v>
@@ -11040,13 +11037,13 @@
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B357" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C357" s="5">
-        <v>46279</v>
+        <v>46267</v>
       </c>
       <c r="D357" s="1" t="s">
         <v>11</v>
@@ -11055,10 +11052,10 @@
         <v>12</v>
       </c>
       <c r="F357" s="1">
-        <v>95</v>
-      </c>
-      <c r="G357" s="6">
-        <v>0.95</v>
+        <v>100</v>
+      </c>
+      <c r="G357" s="2">
+        <v>1</v>
       </c>
       <c r="H357" s="1" t="s">
         <v>37</v>
@@ -11075,7 +11072,7 @@
         <v>10</v>
       </c>
       <c r="C358" s="5">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="D358" s="1" t="s">
         <v>11</v>
@@ -11084,10 +11081,10 @@
         <v>12</v>
       </c>
       <c r="F358" s="1">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="G358" s="2">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="H358" s="1" t="s">
         <v>37</v>
@@ -11104,7 +11101,7 @@
         <v>10</v>
       </c>
       <c r="C359" s="5">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="D359" s="1" t="s">
         <v>11</v>
@@ -11113,10 +11110,10 @@
         <v>12</v>
       </c>
       <c r="F359" s="1">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G359" s="2">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H359" s="1" t="s">
         <v>37</v>
@@ -11133,7 +11130,7 @@
         <v>10</v>
       </c>
       <c r="C360" s="5">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="D360" s="1" t="s">
         <v>11</v>
@@ -11156,13 +11153,13 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B361" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C361" s="5">
-        <v>46266</v>
+        <v>46283</v>
       </c>
       <c r="D361" s="1" t="s">
         <v>11</v>
@@ -11171,10 +11168,10 @@
         <v>12</v>
       </c>
       <c r="F361" s="1">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="G361" s="2">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="H361" s="1" t="s">
         <v>37</v>
@@ -11185,13 +11182,13 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B362" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C362" s="5">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="D362" s="1" t="s">
         <v>11</v>
@@ -11200,10 +11197,10 @@
         <v>12</v>
       </c>
       <c r="F362" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="G362" s="2">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H362" s="1" t="s">
         <v>37</v>
@@ -11214,13 +11211,13 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B363" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C363" s="5">
-        <v>46274</v>
+        <v>46280</v>
       </c>
       <c r="D363" s="1" t="s">
         <v>11</v>
@@ -11243,7 +11240,7 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B364" s="1" t="s">
         <v>19</v>
@@ -11260,7 +11257,7 @@
       <c r="F364" s="1">
         <v>100</v>
       </c>
-      <c r="G364" s="6">
+      <c r="G364" s="2">
         <v>1</v>
       </c>
       <c r="H364" s="1" t="s">
@@ -11272,7 +11269,7 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B365" s="1" t="s">
         <v>19</v>
@@ -11289,7 +11286,7 @@
       <c r="F365" s="1">
         <v>100</v>
       </c>
-      <c r="G365" s="6">
+      <c r="G365" s="2">
         <v>1</v>
       </c>
       <c r="H365" s="1" t="s">
@@ -11301,7 +11298,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B366" s="1" t="s">
         <v>19</v>
@@ -11318,7 +11315,7 @@
       <c r="F366" s="1">
         <v>100</v>
       </c>
-      <c r="G366" s="6">
+      <c r="G366" s="2">
         <v>1</v>
       </c>
       <c r="H366" s="1" t="s">
@@ -11330,13 +11327,13 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B367" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C367" s="5">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D367" s="1" t="s">
         <v>11</v>
@@ -11347,7 +11344,7 @@
       <c r="F367" s="1">
         <v>100</v>
       </c>
-      <c r="G367" s="6">
+      <c r="G367" s="2">
         <v>1</v>
       </c>
       <c r="H367" s="1" t="s">
@@ -11359,7 +11356,7 @@
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B368" s="1" t="s">
         <v>19</v>
@@ -11376,7 +11373,7 @@
       <c r="F368" s="1">
         <v>100</v>
       </c>
-      <c r="G368" s="6">
+      <c r="G368" s="2">
         <v>1</v>
       </c>
       <c r="H368" s="1" t="s">
@@ -11388,13 +11385,13 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B369" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C369" s="5">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D369" s="1" t="s">
         <v>11</v>
@@ -11405,7 +11402,7 @@
       <c r="F369" s="1">
         <v>100</v>
       </c>
-      <c r="G369" s="6">
+      <c r="G369" s="2">
         <v>1</v>
       </c>
       <c r="H369" s="1" t="s">
@@ -11417,13 +11414,13 @@
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B370" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C370" s="5">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="D370" s="1" t="s">
         <v>11</v>
@@ -11434,7 +11431,7 @@
       <c r="F370" s="1">
         <v>100</v>
       </c>
-      <c r="G370" s="6">
+      <c r="G370" s="2">
         <v>1</v>
       </c>
       <c r="H370" s="1" t="s">
@@ -11446,13 +11443,13 @@
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B371" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C371" s="5">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="D371" s="1" t="s">
         <v>11</v>
@@ -11463,7 +11460,7 @@
       <c r="F371" s="1">
         <v>100</v>
       </c>
-      <c r="G371" s="6">
+      <c r="G371" s="2">
         <v>1</v>
       </c>
       <c r="H371" s="1" t="s">
@@ -11475,13 +11472,13 @@
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B372" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C372" s="5">
-        <v>46280</v>
+        <v>46266</v>
       </c>
       <c r="D372" s="1" t="s">
         <v>11</v>
@@ -11490,10 +11487,10 @@
         <v>12</v>
       </c>
       <c r="F372" s="1">
-        <v>100</v>
-      </c>
-      <c r="G372" s="6">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="G372" s="2">
+        <v>0.95</v>
       </c>
       <c r="H372" s="1" t="s">
         <v>37</v>
@@ -11504,13 +11501,13 @@
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B373" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C373" s="5">
-        <v>46281</v>
+        <v>46275</v>
       </c>
       <c r="D373" s="1" t="s">
         <v>11</v>
@@ -11519,10 +11516,10 @@
         <v>12</v>
       </c>
       <c r="F373" s="1">
-        <v>100</v>
-      </c>
-      <c r="G373" s="6">
-        <v>1</v>
+        <v>95</v>
+      </c>
+      <c r="G373" s="2">
+        <v>0.95</v>
       </c>
       <c r="H373" s="1" t="s">
         <v>37</v>
@@ -11533,13 +11530,13 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B374" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C374" s="5">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="D374" s="1" t="s">
         <v>11</v>
@@ -11550,7 +11547,7 @@
       <c r="F374" s="1">
         <v>100</v>
       </c>
-      <c r="G374" s="6">
+      <c r="G374" s="2">
         <v>1</v>
       </c>
       <c r="H374" s="1" t="s">
@@ -11562,13 +11559,13 @@
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B375" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C375" s="5">
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="D375" s="1" t="s">
         <v>11</v>
@@ -11579,7 +11576,7 @@
       <c r="F375" s="1">
         <v>100</v>
       </c>
-      <c r="G375" s="6">
+      <c r="G375" s="2">
         <v>1</v>
       </c>
       <c r="H375" s="1" t="s">
@@ -11591,13 +11588,13 @@
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B376" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C376" s="5">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="D376" s="1" t="s">
         <v>11</v>
@@ -11608,13 +11605,216 @@
       <c r="F376" s="1">
         <v>100</v>
       </c>
-      <c r="G376" s="6">
+      <c r="G376" s="2">
         <v>1</v>
       </c>
       <c r="H376" s="1" t="s">
         <v>37</v>
       </c>
       <c r="I376" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B377" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C377" s="5">
+        <v>46287</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E377" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F377" s="1">
+        <v>100</v>
+      </c>
+      <c r="G377" s="2">
+        <v>1</v>
+      </c>
+      <c r="H377" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I377" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C378" s="5">
+        <v>46288</v>
+      </c>
+      <c r="D378" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E378" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F378" s="1">
+        <v>100</v>
+      </c>
+      <c r="G378" s="2">
+        <v>1</v>
+      </c>
+      <c r="H378" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I378" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B379" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C379" s="5">
+        <v>46288</v>
+      </c>
+      <c r="D379" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E379" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F379" s="1">
+        <v>95</v>
+      </c>
+      <c r="G379" s="2">
+        <v>0.95</v>
+      </c>
+      <c r="H379" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I379" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B380" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C380" s="5">
+        <v>46287</v>
+      </c>
+      <c r="D380" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E380" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F380" s="1">
+        <v>100</v>
+      </c>
+      <c r="G380" s="2">
+        <v>1</v>
+      </c>
+      <c r="H380" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I380" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B381" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C381" s="5">
+        <v>46286</v>
+      </c>
+      <c r="D381" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E381" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F381" s="1">
+        <v>100</v>
+      </c>
+      <c r="G381" s="2">
+        <v>1</v>
+      </c>
+      <c r="H381" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I381" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B382" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C382" s="5">
+        <v>46268</v>
+      </c>
+      <c r="D382" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E382" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F382" s="1">
+        <v>100</v>
+      </c>
+      <c r="G382" s="2">
+        <v>1</v>
+      </c>
+      <c r="H382" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I382" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B383" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C383" s="5">
+        <v>46287</v>
+      </c>
+      <c r="D383" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E383" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F383" s="1">
+        <v>100</v>
+      </c>
+      <c r="G383" s="2">
+        <v>1</v>
+      </c>
+      <c r="H383" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I383" s="1">
         <v>2026</v>
       </c>
     </row>
@@ -12014,6 +12214,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
+    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B7CF5D77C2318A48AE3D01AED053E969" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8bbf009f58139d30e700e9d9dd8708ee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c3d3890c-cedb-4996-8d69-32a58562dce0" xmlns:ns3="081083fe-e475-436e-8ac6-57ab24d1081c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="bbfb5a56ff61f0f4bba1626b54b38306" ns2:_="" ns3:_="">
     <xsd:import namespace="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
@@ -12270,20 +12484,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="081083fe-e475-436e-8ac6-57ab24d1081c" xsi:nil="true"/>
-    <Status xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <Notes xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="c3d3890c-cedb-4996-8d69-32a58562dce0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AAD6C53-AA8B-4861-BD9E-3003633B2469}">
   <ds:schemaRefs>
@@ -12293,6 +12493,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{470B400D-C15B-4808-975D-D6FB017A04F3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -12311,23 +12528,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{810E8512-413E-4D31-94ED-3194BEC41610}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="081083fe-e475-436e-8ac6-57ab24d1081c"/>
-    <ds:schemaRef ds:uri="c3d3890c-cedb-4996-8d69-32a58562dce0"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{4360c1e8-deec-49bb-904e-9331088b2a03}" enabled="0" method="" siteId="{4360c1e8-deec-49bb-904e-9331088b2a03}" removed="1"/>

--- a/MAS_Call_Grading_Raw_Data.xlsx
+++ b/MAS_Call_Grading_Raw_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ansalaza\mas-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6888D363-961D-423C-88B7-5F782EAB4A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3DE8CD1-B3CF-4173-9E20-274E27B9A70A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18405" yWindow="270" windowWidth="20745" windowHeight="20880" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
+    <workbookView xWindow="15255" yWindow="30" windowWidth="36000" windowHeight="20580" xr2:uid="{57776DE4-8F31-45EC-A9ED-7D306CA54141}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Data" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2024" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2074" uniqueCount="66">
   <si>
     <t>AssociateName</t>
   </si>
@@ -241,7 +241,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,13 +264,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E6F5"/>
+        <bgColor rgb="FFC0E6F5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -286,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -299,6 +313,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -346,8 +378,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I383" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:I383" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}" name="tblRawData" displayName="tblRawData" ref="A1:I393" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:I393" xr:uid="{2EF4D820-248F-47FE-A171-6EE7F33C2BAC}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I374">
     <sortCondition ref="A1:A374"/>
   </sortState>
@@ -697,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02E2710C-161E-4D4C-A0A9-FF139CE211A3}">
-  <dimension ref="A1:I383"/>
+  <dimension ref="A1:I393"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27.140625" customWidth="1"/>
@@ -9121,7 +9153,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="0.75" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>17</v>
       </c>
@@ -11815,6 +11847,296 @@
         <v>37</v>
       </c>
       <c r="I383" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B384" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C384" s="8">
+        <v>46281</v>
+      </c>
+      <c r="D384" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E384" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F384" s="6">
+        <v>100</v>
+      </c>
+      <c r="G384" s="10">
+        <v>1</v>
+      </c>
+      <c r="H384" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I384" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B385" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C385" s="9">
+        <v>46283</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E385" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F385" s="7">
+        <v>100</v>
+      </c>
+      <c r="G385" s="11">
+        <v>1</v>
+      </c>
+      <c r="H385" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I385" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B386" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C386" s="9">
+        <v>46281</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F386" s="7">
+        <v>100</v>
+      </c>
+      <c r="G386" s="11">
+        <v>1</v>
+      </c>
+      <c r="H386" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I386" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B387" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C387" s="8">
+        <v>46282</v>
+      </c>
+      <c r="D387" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E387" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F387" s="6">
+        <v>100</v>
+      </c>
+      <c r="G387" s="10">
+        <v>1</v>
+      </c>
+      <c r="H387" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I387" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B388" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C388" s="9">
+        <v>46295</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E388" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F388" s="7">
+        <v>95</v>
+      </c>
+      <c r="G388" s="11">
+        <v>0.95</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I388" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B389" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C389" s="8">
+        <v>46283</v>
+      </c>
+      <c r="D389" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E389" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F389" s="6">
+        <v>95</v>
+      </c>
+      <c r="G389" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="H389" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I389" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B390" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C390" s="9">
+        <v>46289</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E390" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F390" s="7">
+        <v>100</v>
+      </c>
+      <c r="G390" s="11">
+        <v>1</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I390" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B391" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391" s="8">
+        <v>46294</v>
+      </c>
+      <c r="D391" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E391" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F391" s="6">
+        <v>100</v>
+      </c>
+      <c r="G391" s="10">
+        <v>1</v>
+      </c>
+      <c r="H391" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I391" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B392" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C392" s="9">
+        <v>46294</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E392" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F392" s="7">
+        <v>100</v>
+      </c>
+      <c r="G392" s="11">
+        <v>1</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I392" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B393" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C393" s="8">
+        <v>46288</v>
+      </c>
+      <c r="D393" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E393" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F393" s="6">
+        <v>100</v>
+      </c>
+      <c r="G393" s="10">
+        <v>1</v>
+      </c>
+      <c r="H393" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I393" s="6">
         <v>2026</v>
       </c>
     </row>
